--- a/look-samples/v151_cat2_wood_river_client_package.xlsx
+++ b/look-samples/v151_cat2_wood_river_client_package.xlsx
@@ -30,14 +30,14 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'ORG Chart'!$6:$6</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Slicer Hrs'!$A1:$E8</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Slicer Hrs'!$6:$6</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'Staff'!$A1:$P10</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Staff'!$6:$6</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Foremen'!$A1:$P8</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Foremen'!$6:$6</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'Direct'!$A1:$P9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Direct'!$6:$6</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'Support'!$A1:$P8</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="6">'Support'!$6:$6</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Staff'!$A1:$R28</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Staff'!$A:$K,'Staff'!$6:$6</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Foremen'!$A1:$R14</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Foremen'!$A:$K,'Foremen'!$6:$6</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Direct'!$A1:$R28</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Direct'!$A:$K,'Direct'!$6:$6</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'Support'!$A1:$R14</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'Support'!$A:$K,'Support'!$6:$6</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'Equipment Rental'!$A1:$H8</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Equipment Rental'!$6:$6</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="8">'Tensioning Torquing equipment'!$A1:$H8</definedName>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="99">
   <si>
     <t>HIT SQUAD / PROJECT CONTROLS</t>
   </si>
@@ -203,158 +203,171 @@
     <t>TOTAL</t>
   </si>
   <si>
-    <t>Headcount</t>
+    <t>Total Billable</t>
+  </si>
+  <si>
+    <t>Sub Total $</t>
+  </si>
+  <si>
+    <t>Rate</t>
+  </si>
+  <si>
+    <t>Type</t>
   </si>
   <si>
     <t>PD Days</t>
   </si>
   <si>
-    <t>ST Rate</t>
-  </si>
-  <si>
-    <t>OT Rate</t>
-  </si>
-  <si>
-    <t>DT Rate</t>
+    <t>DAYSHIFT</t>
+  </si>
+  <si>
+    <t>HC</t>
+  </si>
+  <si>
+    <t>Enter Hours Per shift Here</t>
+  </si>
+  <si>
+    <t>HPS</t>
+  </si>
+  <si>
+    <t>ST</t>
+  </si>
+  <si>
+    <t>OT</t>
+  </si>
+  <si>
+    <t>DT</t>
+  </si>
+  <si>
+    <t>PD</t>
+  </si>
+  <si>
+    <t>Boilermaker Journeyman</t>
+  </si>
+  <si>
+    <t>NIGHTSHIFT</t>
+  </si>
+  <si>
+    <t>Pipefitter Journeyman</t>
+  </si>
+  <si>
+    <t>Fire Watch</t>
+  </si>
+  <si>
+    <t>Item</t>
+  </si>
+  <si>
+    <t>Period</t>
+  </si>
+  <si>
+    <t>Qty</t>
+  </si>
+  <si>
+    <t>Periods</t>
+  </si>
+  <si>
+    <t>Rate $</t>
+  </si>
+  <si>
+    <t>Freight $</t>
+  </si>
+  <si>
+    <t>Cost $</t>
+  </si>
+  <si>
+    <t>Total $</t>
+  </si>
+  <si>
+    <t>450amp diesel welder</t>
+  </si>
+  <si>
+    <t>daily</t>
+  </si>
+  <si>
+    <t>Hydraulic tensioner</t>
+  </si>
+  <si>
+    <t>Carry deck crane</t>
+  </si>
+  <si>
+    <t>Vendor</t>
+  </si>
+  <si>
+    <t>Scope</t>
+  </si>
+  <si>
+    <t>Affiliate</t>
+  </si>
+  <si>
+    <t>Markup $</t>
+  </si>
+  <si>
+    <t>O&amp;M Crane</t>
+  </si>
+  <si>
+    <t>crane lift</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>AIR MOVER</t>
+  </si>
+  <si>
+    <t>Kind</t>
+  </si>
+  <si>
+    <t>Travelers</t>
+  </si>
+  <si>
+    <t>Miles</t>
+  </si>
+  <si>
+    <t>$ / mile</t>
+  </si>
+  <si>
+    <t>Staff</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Each $</t>
+  </si>
+  <si>
+    <t>Alloy rod</t>
+  </si>
+  <si>
+    <t>Stainless</t>
+  </si>
+  <si>
+    <t>Craft</t>
+  </si>
+  <si>
+    <t>COMP BW $</t>
+  </si>
+  <si>
+    <t>ST Bill $</t>
+  </si>
+  <si>
+    <t>OT Bill $</t>
+  </si>
+  <si>
+    <t>DT Bill $</t>
   </si>
   <si>
     <t>PD Rate</t>
-  </si>
-  <si>
-    <t>ST $</t>
-  </si>
-  <si>
-    <t>OT $</t>
-  </si>
-  <si>
-    <t>DT $</t>
-  </si>
-  <si>
-    <t>PD $</t>
-  </si>
-  <si>
-    <t>Total $</t>
-  </si>
-  <si>
-    <t>MH</t>
-  </si>
-  <si>
-    <t>Boilermaker Journeyman</t>
-  </si>
-  <si>
-    <t>Pipefitter Journeyman</t>
-  </si>
-  <si>
-    <t>Fire Watch</t>
-  </si>
-  <si>
-    <t>Item</t>
-  </si>
-  <si>
-    <t>Period</t>
-  </si>
-  <si>
-    <t>Qty</t>
-  </si>
-  <si>
-    <t>Periods</t>
-  </si>
-  <si>
-    <t>Rate $</t>
-  </si>
-  <si>
-    <t>Freight $</t>
-  </si>
-  <si>
-    <t>Cost $</t>
-  </si>
-  <si>
-    <t>450amp diesel welder</t>
-  </si>
-  <si>
-    <t>daily</t>
-  </si>
-  <si>
-    <t>Hydraulic tensioner</t>
-  </si>
-  <si>
-    <t>Carry deck crane</t>
-  </si>
-  <si>
-    <t>Vendor</t>
-  </si>
-  <si>
-    <t>Scope</t>
-  </si>
-  <si>
-    <t>Affiliate</t>
-  </si>
-  <si>
-    <t>Markup $</t>
-  </si>
-  <si>
-    <t>O&amp;M Crane</t>
-  </si>
-  <si>
-    <t>crane lift</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>AIR MOVER</t>
-  </si>
-  <si>
-    <t>Kind</t>
-  </si>
-  <si>
-    <t>Travelers</t>
-  </si>
-  <si>
-    <t>Miles</t>
-  </si>
-  <si>
-    <t>$ / mile</t>
-  </si>
-  <si>
-    <t>Staff</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Each $</t>
-  </si>
-  <si>
-    <t>Alloy rod</t>
-  </si>
-  <si>
-    <t>Stainless</t>
-  </si>
-  <si>
-    <t>Craft</t>
-  </si>
-  <si>
-    <t>COMP BW $</t>
-  </si>
-  <si>
-    <t>ST Bill $</t>
-  </si>
-  <si>
-    <t>OT Bill $</t>
-  </si>
-  <si>
-    <t>DT Bill $</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
     <numFmt numFmtId="165" formatCode="$#,##0.00"/>
     <numFmt numFmtId="166" formatCode="#,##0.0"/>
+    <numFmt numFmtId="167" formatCode="D-MMM"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -411,7 +424,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -441,6 +454,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF3D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF8E6"/>
       </patternFill>
     </fill>
   </fills>
@@ -474,7 +492,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -511,8 +529,16 @@
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="8" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="8" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="4" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="4" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -896,7 +922,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="6">
-        <v>46269.69564075231</v>
+        <v>46269.70987314815</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -915,10 +941,10 @@
         <v>8</v>
       </c>
       <c r="B7" s="9">
-        <f>Staff!O10</f>
+        <f>Staff!K28</f>
       </c>
       <c r="C7" s="10">
-        <f>Staff!P10</f>
+        <f>Staff!B28</f>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -926,10 +952,10 @@
         <v>9</v>
       </c>
       <c r="B8" s="12">
-        <f>Foremen!O8</f>
+        <f>Foremen!K14</f>
       </c>
       <c r="C8" s="13">
-        <f>Foremen!P8</f>
+        <f>Foremen!B14</f>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -937,10 +963,10 @@
         <v>10</v>
       </c>
       <c r="B9" s="9">
-        <f>Direct!O9</f>
+        <f>Direct!K28</f>
       </c>
       <c r="C9" s="10">
-        <f>Direct!P9</f>
+        <f>Direct!B28</f>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -948,10 +974,10 @@
         <v>11</v>
       </c>
       <c r="B10" s="12">
-        <f>Support!O8</f>
+        <f>Support!K14</f>
       </c>
       <c r="C10" s="13">
-        <f>Support!P8</f>
+        <f>Support!B14</f>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -970,7 +996,7 @@
         <v>13</v>
       </c>
       <c r="B12" s="12">
-        <f>SUM(Staff!N10,Foremen!N8,Direct!N9,Support!N8)</f>
+        <f>SUM(Staff!D28,Foremen!D14,Direct!D28,Support!D14)</f>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -1042,7 +1068,7 @@
         <v>22</v>
       </c>
       <c r="B21" s="17">
-        <v>74.04</v>
+        <v>313.5</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -1127,58 +1153,58 @@
         <v>4</v>
       </c>
       <c r="B5" s="6">
-        <v>46269.69564070602</v>
+        <v>46269.709873125</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C7" s="19">
         <v>1</v>
       </c>
       <c r="D7" s="19">
-        <v>1</v>
-      </c>
-      <c r="E7" s="22">
+        <v>7</v>
+      </c>
+      <c r="E7" s="29">
         <v>400</v>
       </c>
-      <c r="F7" s="22">
+      <c r="F7" s="29">
         <v>0</v>
       </c>
-      <c r="G7" s="22">
+      <c r="G7" s="29">
         <f>C7*D7*E7+F7</f>
       </c>
-      <c r="H7" s="22">
+      <c r="H7" s="29">
         <f>G7*1.06</f>
       </c>
     </row>
@@ -1266,58 +1292,58 @@
         <v>4</v>
       </c>
       <c r="B5" s="6">
-        <v>46269.69564075231</v>
+        <v>46269.70987314815</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C7" s="19">
         <v>1</v>
       </c>
-      <c r="D7" s="22">
+      <c r="D7" s="29">
         <v>500</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="F7" s="22">
+        <v>82</v>
+      </c>
+      <c r="F7" s="29">
         <f>C7*D7</f>
       </c>
-      <c r="G7" s="22">
+      <c r="G7" s="29">
         <f>F7*0.065</f>
       </c>
-      <c r="H7" s="22">
+      <c r="H7" s="29">
         <f>F7+G7</f>
       </c>
     </row>
@@ -1403,52 +1429,52 @@
         <v>4</v>
       </c>
       <c r="B5" s="6">
-        <v>46269.695640729165</v>
+        <v>46269.70987313657</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C7" s="19">
         <v>1</v>
       </c>
       <c r="D7" s="19">
-        <v>1</v>
-      </c>
-      <c r="E7" s="22">
+        <v>7</v>
+      </c>
+      <c r="E7" s="29">
         <v>32</v>
       </c>
-      <c r="F7" s="22">
+      <c r="F7" s="29">
         <v>0</v>
       </c>
-      <c r="G7" s="22">
+      <c r="G7" s="29">
         <f>C7*D7*E7+F7</f>
       </c>
     </row>
@@ -1524,29 +1550,29 @@
         <v>4</v>
       </c>
       <c r="B5" s="6">
-        <v>46269.69564074074</v>
+        <v>46269.70987314815</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B7" s="19">
         <v>3</v>
@@ -1554,10 +1580,10 @@
       <c r="C7" s="19">
         <v>40</v>
       </c>
-      <c r="D7" s="22">
+      <c r="D7" s="29">
         <v>0.7</v>
       </c>
-      <c r="E7" s="22">
+      <c r="E7" s="29">
         <f>B7*C7*D7</f>
       </c>
     </row>
@@ -1634,40 +1660,40 @@
         <v>4</v>
       </c>
       <c r="B5" s="6">
-        <v>46269.69564074074</v>
+        <v>46269.70987314815</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C7" s="19">
         <v>1</v>
       </c>
-      <c r="D7" s="22">
+      <c r="D7" s="29">
         <v>25</v>
       </c>
-      <c r="E7" s="22">
+      <c r="E7" s="29">
         <f>C7*D7</f>
       </c>
     </row>
@@ -1744,46 +1770,46 @@
         <v>4</v>
       </c>
       <c r="B5" s="6">
-        <v>46269.695640555554</v>
+        <v>46269.70987298611</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>52</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="22">
+      <c r="B7" s="29">
         <v>52.5</v>
       </c>
-      <c r="C7" s="22">
+      <c r="C7" s="29">
         <v>91.02</v>
       </c>
-      <c r="D7" s="22">
+      <c r="D7" s="29">
         <v>122.2</v>
       </c>
-      <c r="E7" s="22">
+      <c r="E7" s="29">
         <v>153.39</v>
       </c>
-      <c r="F7" s="22">
+      <c r="F7" s="29">
         <v>140</v>
       </c>
     </row>
@@ -1791,19 +1817,19 @@
       <c r="A8" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="24">
+      <c r="B8" s="30">
         <v>76.5</v>
       </c>
-      <c r="C8" s="24">
+      <c r="C8" s="30">
         <v>121.78</v>
       </c>
-      <c r="D8" s="24">
+      <c r="D8" s="30">
         <v>167.22</v>
       </c>
-      <c r="E8" s="24">
+      <c r="E8" s="30">
         <v>212.67</v>
       </c>
-      <c r="F8" s="24">
+      <c r="F8" s="30">
         <v>140</v>
       </c>
     </row>
@@ -1811,19 +1837,19 @@
       <c r="A9" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="B9" s="22">
+      <c r="B9" s="29">
         <v>58.84</v>
       </c>
-      <c r="C9" s="22">
+      <c r="C9" s="29">
         <v>111.22</v>
       </c>
-      <c r="D9" s="22">
+      <c r="D9" s="29">
         <v>156.31</v>
       </c>
-      <c r="E9" s="22">
+      <c r="E9" s="29">
         <v>201.4</v>
       </c>
-      <c r="F9" s="22">
+      <c r="F9" s="29">
         <v>140</v>
       </c>
     </row>
@@ -1831,59 +1857,59 @@
       <c r="A10" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="24">
+      <c r="B10" s="30">
         <v>49.1</v>
       </c>
-      <c r="C10" s="24">
+      <c r="C10" s="30">
         <v>112.62</v>
       </c>
-      <c r="D10" s="24">
+      <c r="D10" s="30">
         <v>159.07</v>
       </c>
-      <c r="E10" s="24">
+      <c r="E10" s="30">
         <v>205.52</v>
       </c>
-      <c r="F10" s="24">
+      <c r="F10" s="30">
         <v>130</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="B11" s="22">
+        <v>60</v>
+      </c>
+      <c r="B11" s="29">
         <v>45.6</v>
       </c>
-      <c r="C11" s="22">
+      <c r="C11" s="29">
         <v>108.38</v>
       </c>
-      <c r="D11" s="22">
+      <c r="D11" s="29">
         <v>152.78</v>
       </c>
-      <c r="E11" s="22">
+      <c r="E11" s="29">
         <v>197.19</v>
       </c>
-      <c r="F11" s="22">
+      <c r="F11" s="29">
         <v>130</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="B12" s="22">
+        <v>62</v>
+      </c>
+      <c r="B12" s="29">
         <v>49.03</v>
       </c>
-      <c r="C12" s="22">
+      <c r="C12" s="29">
         <v>99.33</v>
       </c>
-      <c r="D12" s="22">
+      <c r="D12" s="29">
         <v>138.69</v>
       </c>
-      <c r="E12" s="22">
+      <c r="E12" s="29">
         <v>178.05</v>
       </c>
-      <c r="F12" s="22">
+      <c r="F12" s="29">
         <v>130</v>
       </c>
     </row>
@@ -1952,7 +1978,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="6">
-        <v>46269.695640694445</v>
+        <v>46269.70987310185</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2118,7 +2144,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="6">
-        <v>46269.69564070602</v>
+        <v>46269.709873125</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2143,13 +2169,13 @@
         <v>45</v>
       </c>
       <c r="B7" s="21">
-        <v>100</v>
+        <v>580</v>
       </c>
       <c r="C7" s="21">
-        <v>20</v>
+        <v>260</v>
       </c>
       <c r="D7" s="21">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="E7" s="21">
         <f>B7+C7+D7</f>
@@ -2193,17 +2219,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF1F8A96"/>
-    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:R28"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="32" customWidth="1"/>
-    <col min="2" max="6" width="12" customWidth="1"/>
-    <col min="7" max="16" width="14" customWidth="1"/>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="26" customWidth="1"/>
+    <col min="4" max="5" width="14" customWidth="1"/>
+    <col min="6" max="10" width="12" customWidth="1"/>
+    <col min="11" max="11" width="14" customWidth="1"/>
+    <col min="12" max="18" width="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" ht="22" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2222,13 +2251,15 @@
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -2247,6 +2278,8 @@
       <c r="N3" s="3"/>
       <c r="O3" s="3"/>
       <c r="P3" s="3"/>
+      <c r="Q3" s="3"/>
+      <c r="R3" s="3"/>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
@@ -2258,252 +2291,771 @@
         <v>4</v>
       </c>
       <c r="B5" s="6">
-        <v>46269.69564064815</v>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+        <v>46269.70987305556</v>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>47</v>
       </c>
       <c r="C6" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="G6" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="H6" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="I6" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="F6" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="I6" s="7" t="s">
+      <c r="J6" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="J6" s="7" t="s">
+      <c r="K6" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="L6" s="22">
+        <v>46266</v>
+      </c>
+      <c r="M6" s="22">
+        <f>L6+1</f>
+      </c>
+      <c r="N6" s="22">
+        <f>M6+1</f>
+      </c>
+      <c r="O6" s="22">
+        <f>N6+1</f>
+      </c>
+      <c r="P6" s="22">
+        <f>O6+1</f>
+      </c>
+      <c r="Q6" s="22">
+        <f>P6+1</f>
+      </c>
+      <c r="R6" s="22">
+        <f>Q6+1</f>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="K6" s="7" t="s">
+      <c r="B7" s="24">
+        <f>G7+H7+I7</f>
+      </c>
+      <c r="C7" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="25">
+        <f>K7</f>
+      </c>
+      <c r="G7" s="24">
+        <f>B10</f>
+      </c>
+      <c r="H7" s="24">
+        <f>B11</f>
+      </c>
+      <c r="I7" s="24">
+        <f>B12</f>
+      </c>
+      <c r="J7" s="24">
+        <f>B13</f>
+      </c>
+      <c r="K7" s="25">
+        <f>D10+D11+D12</f>
+      </c>
+    </row>
+    <row r="8" spans="6:18" x14ac:dyDescent="0.25">
+      <c r="F8" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="L6" s="7" t="s">
+      <c r="L8" s="27">
+        <v>1</v>
+      </c>
+      <c r="M8" s="27">
+        <v>1</v>
+      </c>
+      <c r="N8" s="27">
+        <v>1</v>
+      </c>
+      <c r="O8" s="27">
+        <v>1</v>
+      </c>
+      <c r="P8" s="27">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="27">
+        <v>1</v>
+      </c>
+      <c r="R8" s="27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A9" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="M6" s="7" t="s">
+      <c r="F9" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="N6" s="7" t="s">
+      <c r="L9" s="28">
+        <v>10</v>
+      </c>
+      <c r="M9" s="28">
+        <v>10</v>
+      </c>
+      <c r="N9" s="28">
+        <v>10</v>
+      </c>
+      <c r="O9" s="28">
+        <v>10</v>
+      </c>
+      <c r="P9" s="28">
+        <v>10</v>
+      </c>
+      <c r="Q9" s="28">
+        <v>10</v>
+      </c>
+      <c r="R9" s="28">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B10" s="21">
+        <f>SUM(L10:R10)</f>
+      </c>
+      <c r="D10" s="29">
+        <f>B10*E10</f>
+      </c>
+      <c r="E10" s="29">
+        <f>'Rate Tables'!C7</f>
+      </c>
+      <c r="F10" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="O6" s="7" t="s">
+      <c r="L10" s="21">
+        <f>IF(L$6="","",IF(WEEKDAY(L$6,1)=1,0,MIN(10,L9)*L8))</f>
+      </c>
+      <c r="M10" s="21">
+        <f>IF(M$6="","",IF(WEEKDAY(M$6,1)=1,0,MIN(10,M9)*M8))</f>
+      </c>
+      <c r="N10" s="21">
+        <f>IF(N$6="","",IF(WEEKDAY(N$6,1)=1,0,MIN(10,N9)*N8))</f>
+      </c>
+      <c r="O10" s="21">
+        <f>IF(O$6="","",IF(WEEKDAY(O$6,1)=1,0,MIN(10,O9)*O8))</f>
+      </c>
+      <c r="P10" s="21">
+        <f>IF(P$6="","",IF(WEEKDAY(P$6,1)=1,0,MIN(10,P9)*P8))</f>
+      </c>
+      <c r="Q10" s="21">
+        <f>IF(Q$6="","",IF(WEEKDAY(Q$6,1)=1,0,MIN(10,Q9)*Q8))</f>
+      </c>
+      <c r="R10" s="21">
+        <f>IF(R$6="","",IF(WEEKDAY(R$6,1)=1,0,MIN(10,R9)*R8))</f>
+      </c>
+    </row>
+    <row r="11" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B11" s="21">
+        <f>SUM(L11:R11)</f>
+      </c>
+      <c r="D11" s="29">
+        <f>B11*E11</f>
+      </c>
+      <c r="E11" s="29">
+        <f>'Rate Tables'!D7</f>
+      </c>
+      <c r="F11" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="P6" s="7" t="s">
+      <c r="L11" s="21">
+        <f>IF(L$6="","",IF(WEEKDAY(L$6,1)=1,0,MAX(0,L9-10)*L8))</f>
+      </c>
+      <c r="M11" s="21">
+        <f>IF(M$6="","",IF(WEEKDAY(M$6,1)=1,0,MAX(0,M9-10)*M8))</f>
+      </c>
+      <c r="N11" s="21">
+        <f>IF(N$6="","",IF(WEEKDAY(N$6,1)=1,0,MAX(0,N9-10)*N8))</f>
+      </c>
+      <c r="O11" s="21">
+        <f>IF(O$6="","",IF(WEEKDAY(O$6,1)=1,0,MAX(0,O9-10)*O8))</f>
+      </c>
+      <c r="P11" s="21">
+        <f>IF(P$6="","",IF(WEEKDAY(P$6,1)=1,0,MAX(0,P9-10)*P8))</f>
+      </c>
+      <c r="Q11" s="21">
+        <f>IF(Q$6="","",IF(WEEKDAY(Q$6,1)=1,0,MAX(0,Q9-10)*Q8))</f>
+      </c>
+      <c r="R11" s="21">
+        <f>IF(R$6="","",IF(WEEKDAY(R$6,1)=1,0,MAX(0,R9-10)*R8))</f>
+      </c>
+    </row>
+    <row r="12" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B12" s="21">
+        <f>SUM(L12:R12)</f>
+      </c>
+      <c r="D12" s="29">
+        <f>B12*E12</f>
+      </c>
+      <c r="E12" s="29">
+        <f>'Rate Tables'!E7</f>
+      </c>
+      <c r="F12" s="8" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B7" s="19">
-        <v>1</v>
-      </c>
-      <c r="C7" s="21">
-        <v>10</v>
-      </c>
-      <c r="D7" s="21">
-        <v>0</v>
-      </c>
-      <c r="E7" s="21">
-        <v>0</v>
-      </c>
-      <c r="F7" s="21">
-        <v>1</v>
-      </c>
-      <c r="G7" s="22">
-        <f>'Rate Tables'!C7</f>
-      </c>
-      <c r="H7" s="22">
-        <f>'Rate Tables'!D7</f>
-      </c>
-      <c r="I7" s="22">
-        <f>'Rate Tables'!E7</f>
-      </c>
-      <c r="J7" s="22">
+      <c r="L12" s="21">
+        <f>IF(L$6="","",IF(WEEKDAY(L$6,1)=1,L9*L8,0))</f>
+      </c>
+      <c r="M12" s="21">
+        <f>IF(M$6="","",IF(WEEKDAY(M$6,1)=1,M9*M8,0))</f>
+      </c>
+      <c r="N12" s="21">
+        <f>IF(N$6="","",IF(WEEKDAY(N$6,1)=1,N9*N8,0))</f>
+      </c>
+      <c r="O12" s="21">
+        <f>IF(O$6="","",IF(WEEKDAY(O$6,1)=1,O9*O8,0))</f>
+      </c>
+      <c r="P12" s="21">
+        <f>IF(P$6="","",IF(WEEKDAY(P$6,1)=1,P9*P8,0))</f>
+      </c>
+      <c r="Q12" s="21">
+        <f>IF(Q$6="","",IF(WEEKDAY(Q$6,1)=1,Q9*Q8,0))</f>
+      </c>
+      <c r="R12" s="21">
+        <f>IF(R$6="","",IF(WEEKDAY(R$6,1)=1,R9*R8,0))</f>
+      </c>
+    </row>
+    <row r="13" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B13" s="21">
+        <f>SUM(L13:R13)</f>
+      </c>
+      <c r="D13" s="29">
+        <f>B13*E13</f>
+      </c>
+      <c r="E13" s="29">
         <v>140</v>
       </c>
-      <c r="K7" s="22">
-        <f>C7*G7</f>
-      </c>
-      <c r="L7" s="22">
-        <f>D7*H7</f>
-      </c>
-      <c r="M7" s="22">
-        <f>E7*I7</f>
-      </c>
-      <c r="N7" s="22">
-        <f>F7*J7</f>
-      </c>
-      <c r="O7" s="22">
-        <f>K7+L7+M7</f>
-      </c>
-      <c r="P7" s="21">
-        <f>C7+D7+E7</f>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" s="11" t="s">
+      <c r="F13" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="L13" s="19">
+        <v>1</v>
+      </c>
+      <c r="M13" s="19">
+        <v>1</v>
+      </c>
+      <c r="N13" s="19">
+        <v>1</v>
+      </c>
+      <c r="O13" s="19">
+        <v>1</v>
+      </c>
+      <c r="P13" s="19">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="19">
+        <v>1</v>
+      </c>
+      <c r="R13" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="B14" s="24">
+        <f>G14+H14+I14</f>
+      </c>
+      <c r="C14" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="20">
-        <v>1</v>
-      </c>
-      <c r="C8" s="23">
-        <v>10</v>
-      </c>
-      <c r="D8" s="23">
-        <v>0</v>
-      </c>
-      <c r="E8" s="23">
-        <v>0</v>
-      </c>
-      <c r="F8" s="23">
-        <v>1</v>
-      </c>
-      <c r="G8" s="24">
+      <c r="D14" s="25">
+        <f>K14</f>
+      </c>
+      <c r="G14" s="24">
+        <f>B17</f>
+      </c>
+      <c r="H14" s="24">
+        <f>B18</f>
+      </c>
+      <c r="I14" s="24">
+        <f>B19</f>
+      </c>
+      <c r="J14" s="24">
+        <f>B20</f>
+      </c>
+      <c r="K14" s="25">
+        <f>D17+D18+D19</f>
+      </c>
+    </row>
+    <row r="15" spans="6:18" x14ac:dyDescent="0.25">
+      <c r="F15" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="L15" s="27">
+        <v>1</v>
+      </c>
+      <c r="M15" s="27">
+        <v>1</v>
+      </c>
+      <c r="N15" s="27">
+        <v>1</v>
+      </c>
+      <c r="O15" s="27">
+        <v>1</v>
+      </c>
+      <c r="P15" s="27">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="27">
+        <v>1</v>
+      </c>
+      <c r="R15" s="27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A16" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="F16" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="L16" s="28">
+        <v>10</v>
+      </c>
+      <c r="M16" s="28">
+        <v>10</v>
+      </c>
+      <c r="N16" s="28">
+        <v>10</v>
+      </c>
+      <c r="O16" s="28">
+        <v>10</v>
+      </c>
+      <c r="P16" s="28">
+        <v>10</v>
+      </c>
+      <c r="Q16" s="28">
+        <v>10</v>
+      </c>
+      <c r="R16" s="28">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B17" s="21">
+        <f>SUM(L17:R17)</f>
+      </c>
+      <c r="D17" s="29">
+        <f>B17*E17</f>
+      </c>
+      <c r="E17" s="29">
         <f>'Rate Tables'!C8</f>
       </c>
-      <c r="H8" s="24">
+      <c r="F17" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="L17" s="21">
+        <f>IF(L$6="","",IF(WEEKDAY(L$6,1)=1,0,MIN(10,L16)*L15))</f>
+      </c>
+      <c r="M17" s="21">
+        <f>IF(M$6="","",IF(WEEKDAY(M$6,1)=1,0,MIN(10,M16)*M15))</f>
+      </c>
+      <c r="N17" s="21">
+        <f>IF(N$6="","",IF(WEEKDAY(N$6,1)=1,0,MIN(10,N16)*N15))</f>
+      </c>
+      <c r="O17" s="21">
+        <f>IF(O$6="","",IF(WEEKDAY(O$6,1)=1,0,MIN(10,O16)*O15))</f>
+      </c>
+      <c r="P17" s="21">
+        <f>IF(P$6="","",IF(WEEKDAY(P$6,1)=1,0,MIN(10,P16)*P15))</f>
+      </c>
+      <c r="Q17" s="21">
+        <f>IF(Q$6="","",IF(WEEKDAY(Q$6,1)=1,0,MIN(10,Q16)*Q15))</f>
+      </c>
+      <c r="R17" s="21">
+        <f>IF(R$6="","",IF(WEEKDAY(R$6,1)=1,0,MIN(10,R16)*R15))</f>
+      </c>
+    </row>
+    <row r="18" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B18" s="21">
+        <f>SUM(L18:R18)</f>
+      </c>
+      <c r="D18" s="29">
+        <f>B18*E18</f>
+      </c>
+      <c r="E18" s="29">
         <f>'Rate Tables'!D8</f>
       </c>
-      <c r="I8" s="24">
+      <c r="F18" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="L18" s="21">
+        <f>IF(L$6="","",IF(WEEKDAY(L$6,1)=1,0,MAX(0,L16-10)*L15))</f>
+      </c>
+      <c r="M18" s="21">
+        <f>IF(M$6="","",IF(WEEKDAY(M$6,1)=1,0,MAX(0,M16-10)*M15))</f>
+      </c>
+      <c r="N18" s="21">
+        <f>IF(N$6="","",IF(WEEKDAY(N$6,1)=1,0,MAX(0,N16-10)*N15))</f>
+      </c>
+      <c r="O18" s="21">
+        <f>IF(O$6="","",IF(WEEKDAY(O$6,1)=1,0,MAX(0,O16-10)*O15))</f>
+      </c>
+      <c r="P18" s="21">
+        <f>IF(P$6="","",IF(WEEKDAY(P$6,1)=1,0,MAX(0,P16-10)*P15))</f>
+      </c>
+      <c r="Q18" s="21">
+        <f>IF(Q$6="","",IF(WEEKDAY(Q$6,1)=1,0,MAX(0,Q16-10)*Q15))</f>
+      </c>
+      <c r="R18" s="21">
+        <f>IF(R$6="","",IF(WEEKDAY(R$6,1)=1,0,MAX(0,R16-10)*R15))</f>
+      </c>
+    </row>
+    <row r="19" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B19" s="21">
+        <f>SUM(L19:R19)</f>
+      </c>
+      <c r="D19" s="29">
+        <f>B19*E19</f>
+      </c>
+      <c r="E19" s="29">
         <f>'Rate Tables'!E8</f>
       </c>
-      <c r="J8" s="24">
+      <c r="F19" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="L19" s="21">
+        <f>IF(L$6="","",IF(WEEKDAY(L$6,1)=1,L16*L15,0))</f>
+      </c>
+      <c r="M19" s="21">
+        <f>IF(M$6="","",IF(WEEKDAY(M$6,1)=1,M16*M15,0))</f>
+      </c>
+      <c r="N19" s="21">
+        <f>IF(N$6="","",IF(WEEKDAY(N$6,1)=1,N16*N15,0))</f>
+      </c>
+      <c r="O19" s="21">
+        <f>IF(O$6="","",IF(WEEKDAY(O$6,1)=1,O16*O15,0))</f>
+      </c>
+      <c r="P19" s="21">
+        <f>IF(P$6="","",IF(WEEKDAY(P$6,1)=1,P16*P15,0))</f>
+      </c>
+      <c r="Q19" s="21">
+        <f>IF(Q$6="","",IF(WEEKDAY(Q$6,1)=1,Q16*Q15,0))</f>
+      </c>
+      <c r="R19" s="21">
+        <f>IF(R$6="","",IF(WEEKDAY(R$6,1)=1,R16*R15,0))</f>
+      </c>
+    </row>
+    <row r="20" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B20" s="21">
+        <f>SUM(L20:R20)</f>
+      </c>
+      <c r="D20" s="29">
+        <f>B20*E20</f>
+      </c>
+      <c r="E20" s="29">
         <v>140</v>
       </c>
-      <c r="K8" s="24">
-        <f>C8*G8</f>
-      </c>
-      <c r="L8" s="24">
-        <f>D8*H8</f>
-      </c>
-      <c r="M8" s="24">
-        <f>E8*I8</f>
-      </c>
-      <c r="N8" s="24">
-        <f>F8*J8</f>
-      </c>
-      <c r="O8" s="24">
-        <f>K8+L8+M8</f>
-      </c>
-      <c r="P8" s="23">
-        <f>C8+D8+E8</f>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" s="8" t="s">
+      <c r="F20" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="L20" s="19">
+        <v>1</v>
+      </c>
+      <c r="M20" s="19">
+        <v>1</v>
+      </c>
+      <c r="N20" s="19">
+        <v>1</v>
+      </c>
+      <c r="O20" s="19">
+        <v>1</v>
+      </c>
+      <c r="P20" s="19">
+        <v>1</v>
+      </c>
+      <c r="Q20" s="19">
+        <v>1</v>
+      </c>
+      <c r="R20" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="B21" s="24">
+        <f>G21+H21+I21</f>
+      </c>
+      <c r="C21" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="B9" s="19">
-        <v>1</v>
-      </c>
-      <c r="C9" s="21">
-        <v>8</v>
-      </c>
-      <c r="D9" s="21">
-        <v>2</v>
-      </c>
-      <c r="E9" s="21">
-        <v>0</v>
-      </c>
-      <c r="F9" s="21">
-        <v>1</v>
-      </c>
-      <c r="G9" s="22">
+      <c r="D21" s="25">
+        <f>K21</f>
+      </c>
+      <c r="G21" s="24">
+        <f>B24</f>
+      </c>
+      <c r="H21" s="24">
+        <f>B25</f>
+      </c>
+      <c r="I21" s="24">
+        <f>B26</f>
+      </c>
+      <c r="J21" s="24">
+        <f>B27</f>
+      </c>
+      <c r="K21" s="25">
+        <f>D24+D25+D26</f>
+      </c>
+    </row>
+    <row r="22" spans="6:18" x14ac:dyDescent="0.25">
+      <c r="F22" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="L22" s="27">
+        <v>1</v>
+      </c>
+      <c r="M22" s="27">
+        <v>1</v>
+      </c>
+      <c r="N22" s="27">
+        <v>1</v>
+      </c>
+      <c r="O22" s="27">
+        <v>1</v>
+      </c>
+      <c r="P22" s="27">
+        <v>1</v>
+      </c>
+      <c r="Q22" s="27">
+        <v>1</v>
+      </c>
+      <c r="R22" s="27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A23" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="F23" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="L23" s="28">
+        <v>10</v>
+      </c>
+      <c r="M23" s="28">
+        <v>10</v>
+      </c>
+      <c r="N23" s="28">
+        <v>10</v>
+      </c>
+      <c r="O23" s="28">
+        <v>10</v>
+      </c>
+      <c r="P23" s="28">
+        <v>10</v>
+      </c>
+      <c r="Q23" s="28">
+        <v>10</v>
+      </c>
+      <c r="R23" s="28">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B24" s="21">
+        <f>SUM(L24:R24)</f>
+      </c>
+      <c r="D24" s="29">
+        <f>B24*E24</f>
+      </c>
+      <c r="E24" s="29">
         <f>'Rate Tables'!C9</f>
       </c>
-      <c r="H9" s="22">
+      <c r="F24" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="L24" s="21">
+        <f>IF(L$6="","",IF(OR(WEEKDAY(L$6,1)=1,WEEKDAY(L$6,1)=7),0,MIN(8,L23)*L22))</f>
+      </c>
+      <c r="M24" s="21">
+        <f>IF(M$6="","",IF(OR(WEEKDAY(M$6,1)=1,WEEKDAY(M$6,1)=7),0,MIN(8,M23)*M22))</f>
+      </c>
+      <c r="N24" s="21">
+        <f>IF(N$6="","",IF(OR(WEEKDAY(N$6,1)=1,WEEKDAY(N$6,1)=7),0,MIN(8,N23)*N22))</f>
+      </c>
+      <c r="O24" s="21">
+        <f>IF(O$6="","",IF(OR(WEEKDAY(O$6,1)=1,WEEKDAY(O$6,1)=7),0,MIN(8,O23)*O22))</f>
+      </c>
+      <c r="P24" s="21">
+        <f>IF(P$6="","",IF(OR(WEEKDAY(P$6,1)=1,WEEKDAY(P$6,1)=7),0,MIN(8,P23)*P22))</f>
+      </c>
+      <c r="Q24" s="21">
+        <f>IF(Q$6="","",IF(OR(WEEKDAY(Q$6,1)=1,WEEKDAY(Q$6,1)=7),0,MIN(8,Q23)*Q22))</f>
+      </c>
+      <c r="R24" s="21">
+        <f>IF(R$6="","",IF(OR(WEEKDAY(R$6,1)=1,WEEKDAY(R$6,1)=7),0,MIN(8,R23)*R22))</f>
+      </c>
+    </row>
+    <row r="25" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B25" s="21">
+        <f>SUM(L25:R25)</f>
+      </c>
+      <c r="D25" s="29">
+        <f>B25*E25</f>
+      </c>
+      <c r="E25" s="29">
         <f>'Rate Tables'!D9</f>
       </c>
-      <c r="I9" s="22">
+      <c r="F25" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="L25" s="21">
+        <f>IF(L$6="","",IF(WEEKDAY(L$6,1)=1,0,IF(WEEKDAY(L$6,1)=7,L23*L22,MAX(0,L23-8)*L22)))</f>
+      </c>
+      <c r="M25" s="21">
+        <f>IF(M$6="","",IF(WEEKDAY(M$6,1)=1,0,IF(WEEKDAY(M$6,1)=7,M23*M22,MAX(0,M23-8)*M22)))</f>
+      </c>
+      <c r="N25" s="21">
+        <f>IF(N$6="","",IF(WEEKDAY(N$6,1)=1,0,IF(WEEKDAY(N$6,1)=7,N23*N22,MAX(0,N23-8)*N22)))</f>
+      </c>
+      <c r="O25" s="21">
+        <f>IF(O$6="","",IF(WEEKDAY(O$6,1)=1,0,IF(WEEKDAY(O$6,1)=7,O23*O22,MAX(0,O23-8)*O22)))</f>
+      </c>
+      <c r="P25" s="21">
+        <f>IF(P$6="","",IF(WEEKDAY(P$6,1)=1,0,IF(WEEKDAY(P$6,1)=7,P23*P22,MAX(0,P23-8)*P22)))</f>
+      </c>
+      <c r="Q25" s="21">
+        <f>IF(Q$6="","",IF(WEEKDAY(Q$6,1)=1,0,IF(WEEKDAY(Q$6,1)=7,Q23*Q22,MAX(0,Q23-8)*Q22)))</f>
+      </c>
+      <c r="R25" s="21">
+        <f>IF(R$6="","",IF(WEEKDAY(R$6,1)=1,0,IF(WEEKDAY(R$6,1)=7,R23*R22,MAX(0,R23-8)*R22)))</f>
+      </c>
+    </row>
+    <row r="26" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B26" s="21">
+        <f>SUM(L26:R26)</f>
+      </c>
+      <c r="D26" s="29">
+        <f>B26*E26</f>
+      </c>
+      <c r="E26" s="29">
         <f>'Rate Tables'!E9</f>
       </c>
-      <c r="J9" s="22">
+      <c r="F26" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="L26" s="21">
+        <f>IF(L$6="","",IF(WEEKDAY(L$6,1)=1,L23*L22,0))</f>
+      </c>
+      <c r="M26" s="21">
+        <f>IF(M$6="","",IF(WEEKDAY(M$6,1)=1,M23*M22,0))</f>
+      </c>
+      <c r="N26" s="21">
+        <f>IF(N$6="","",IF(WEEKDAY(N$6,1)=1,N23*N22,0))</f>
+      </c>
+      <c r="O26" s="21">
+        <f>IF(O$6="","",IF(WEEKDAY(O$6,1)=1,O23*O22,0))</f>
+      </c>
+      <c r="P26" s="21">
+        <f>IF(P$6="","",IF(WEEKDAY(P$6,1)=1,P23*P22,0))</f>
+      </c>
+      <c r="Q26" s="21">
+        <f>IF(Q$6="","",IF(WEEKDAY(Q$6,1)=1,Q23*Q22,0))</f>
+      </c>
+      <c r="R26" s="21">
+        <f>IF(R$6="","",IF(WEEKDAY(R$6,1)=1,R23*R22,0))</f>
+      </c>
+    </row>
+    <row r="27" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B27" s="21">
+        <f>SUM(L27:R27)</f>
+      </c>
+      <c r="D27" s="29">
+        <f>B27*E27</f>
+      </c>
+      <c r="E27" s="29">
         <v>140</v>
       </c>
-      <c r="K9" s="22">
-        <f>C9*G9</f>
-      </c>
-      <c r="L9" s="22">
-        <f>D9*H9</f>
-      </c>
-      <c r="M9" s="22">
-        <f>E9*I9</f>
-      </c>
-      <c r="N9" s="22">
-        <f>F9*J9</f>
-      </c>
-      <c r="O9" s="22">
-        <f>K9+L9+M9</f>
-      </c>
-      <c r="P9" s="21">
-        <f>C9+D9+E9</f>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" s="14" t="s">
+      <c r="F27" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="L27" s="19">
+        <v>1</v>
+      </c>
+      <c r="M27" s="19">
+        <v>1</v>
+      </c>
+      <c r="N27" s="19">
+        <v>1</v>
+      </c>
+      <c r="O27" s="19">
+        <v>1</v>
+      </c>
+      <c r="P27" s="19">
+        <v>1</v>
+      </c>
+      <c r="Q27" s="19">
+        <v>1</v>
+      </c>
+      <c r="R27" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="C10" s="15">
-        <f>SUM(C7:C9)</f>
-      </c>
-      <c r="D10" s="15">
-        <f>SUM(D7:D9)</f>
-      </c>
-      <c r="E10" s="15">
-        <f>SUM(E7:E9)</f>
-      </c>
-      <c r="F10" s="15">
-        <f>SUM(F7:F9)</f>
-      </c>
-      <c r="K10" s="18">
-        <f>SUM(K7:K9)</f>
-      </c>
-      <c r="L10" s="18">
-        <f>SUM(L7:L9)</f>
-      </c>
-      <c r="M10" s="18">
-        <f>SUM(M7:M9)</f>
-      </c>
-      <c r="N10" s="18">
-        <f>SUM(N7:N9)</f>
-      </c>
-      <c r="O10" s="18">
-        <f>SUM(O7:O9)</f>
-      </c>
-      <c r="P10" s="15">
-        <f>SUM(P7:P9)</f>
+      <c r="B28" s="15">
+        <f>SUM(B7,B14,B21)</f>
+      </c>
+      <c r="D28" s="18">
+        <f>SUM(D13,D20,D27)</f>
+      </c>
+      <c r="G28" s="15">
+        <f>SUM(G7,G14,G21)</f>
+      </c>
+      <c r="H28" s="15">
+        <f>SUM(H7,H14,H21)</f>
+      </c>
+      <c r="I28" s="15">
+        <f>SUM(I7,I14,I21)</f>
+      </c>
+      <c r="J28" s="15">
+        <f>SUM(J7,J14,J21)</f>
+      </c>
+      <c r="K28" s="18">
+        <f>SUM(K7,K14,K21)</f>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="A3:P3"/>
+    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="A3:R3"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.65" bottom="0.65" header="0.28" footer="0.28"/>
-  <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="20"/>
+  <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;B HIT SQUAD / PROJECT CONTROLS &amp;C Staff &amp;R Confidential</oddHeader>
     <oddFooter>&amp;L Produced by Hit Squad Project Controls &amp;C &amp;D &amp;R Page &amp;P of &amp;N</oddFooter>
@@ -2517,17 +3069,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF1F8A96"/>
-    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P8"/>
+  <dimension ref="A1:R14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="32" customWidth="1"/>
-    <col min="2" max="6" width="12" customWidth="1"/>
-    <col min="7" max="16" width="14" customWidth="1"/>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="26" customWidth="1"/>
+    <col min="4" max="5" width="14" customWidth="1"/>
+    <col min="6" max="10" width="12" customWidth="1"/>
+    <col min="11" max="11" width="14" customWidth="1"/>
+    <col min="12" max="18" width="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" ht="22" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2546,13 +3101,15 @@
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -2571,6 +3128,8 @@
       <c r="N3" s="3"/>
       <c r="O3" s="3"/>
       <c r="P3" s="3"/>
+      <c r="Q3" s="3"/>
+      <c r="R3" s="3"/>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
@@ -2582,152 +3141,323 @@
         <v>4</v>
       </c>
       <c r="B5" s="6">
-        <v>46269.6956406713</v>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+        <v>46269.709873078704</v>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>47</v>
       </c>
       <c r="C6" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="G6" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="H6" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="I6" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="F6" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="I6" s="7" t="s">
+      <c r="J6" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="J6" s="7" t="s">
+      <c r="K6" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="L6" s="22">
+        <v>46266</v>
+      </c>
+      <c r="M6" s="22">
+        <f>L6+1</f>
+      </c>
+      <c r="N6" s="22">
+        <f>M6+1</f>
+      </c>
+      <c r="O6" s="22">
+        <f>N6+1</f>
+      </c>
+      <c r="P6" s="22">
+        <f>O6+1</f>
+      </c>
+      <c r="Q6" s="22">
+        <f>P6+1</f>
+      </c>
+      <c r="R6" s="22">
+        <f>Q6+1</f>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="K6" s="7" t="s">
+      <c r="B7" s="24">
+        <f>G7+H7+I7</f>
+      </c>
+      <c r="C7" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" s="25">
+        <f>K7</f>
+      </c>
+      <c r="G7" s="24">
+        <f>B10</f>
+      </c>
+      <c r="H7" s="24">
+        <f>B11</f>
+      </c>
+      <c r="I7" s="24">
+        <f>B12</f>
+      </c>
+      <c r="J7" s="24">
+        <f>B13</f>
+      </c>
+      <c r="K7" s="25">
+        <f>D10+D11+D12</f>
+      </c>
+    </row>
+    <row r="8" spans="6:18" x14ac:dyDescent="0.25">
+      <c r="F8" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="L6" s="7" t="s">
+      <c r="L8" s="27">
+        <v>1</v>
+      </c>
+      <c r="M8" s="27">
+        <v>1</v>
+      </c>
+      <c r="N8" s="27">
+        <v>1</v>
+      </c>
+      <c r="O8" s="27">
+        <v>1</v>
+      </c>
+      <c r="P8" s="27">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="27">
+        <v>1</v>
+      </c>
+      <c r="R8" s="27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A9" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="M6" s="7" t="s">
+      <c r="F9" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="N6" s="7" t="s">
+      <c r="L9" s="28">
+        <v>10</v>
+      </c>
+      <c r="M9" s="28">
+        <v>10</v>
+      </c>
+      <c r="N9" s="28">
+        <v>10</v>
+      </c>
+      <c r="O9" s="28">
+        <v>10</v>
+      </c>
+      <c r="P9" s="28">
+        <v>10</v>
+      </c>
+      <c r="Q9" s="28">
+        <v>10</v>
+      </c>
+      <c r="R9" s="28">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B10" s="21">
+        <f>SUM(L10:R10)</f>
+      </c>
+      <c r="D10" s="29">
+        <f>B10*E10</f>
+      </c>
+      <c r="E10" s="29">
+        <f>'Rate Tables'!C10</f>
+      </c>
+      <c r="F10" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="O6" s="7" t="s">
+      <c r="L10" s="21">
+        <f>IF(L$6="","",IF(OR(WEEKDAY(L$6,1)=1,WEEKDAY(L$6,1)=7),0,MIN(8,L9)*L8))</f>
+      </c>
+      <c r="M10" s="21">
+        <f>IF(M$6="","",IF(OR(WEEKDAY(M$6,1)=1,WEEKDAY(M$6,1)=7),0,MIN(8,M9)*M8))</f>
+      </c>
+      <c r="N10" s="21">
+        <f>IF(N$6="","",IF(OR(WEEKDAY(N$6,1)=1,WEEKDAY(N$6,1)=7),0,MIN(8,N9)*N8))</f>
+      </c>
+      <c r="O10" s="21">
+        <f>IF(O$6="","",IF(OR(WEEKDAY(O$6,1)=1,WEEKDAY(O$6,1)=7),0,MIN(8,O9)*O8))</f>
+      </c>
+      <c r="P10" s="21">
+        <f>IF(P$6="","",IF(OR(WEEKDAY(P$6,1)=1,WEEKDAY(P$6,1)=7),0,MIN(8,P9)*P8))</f>
+      </c>
+      <c r="Q10" s="21">
+        <f>IF(Q$6="","",IF(OR(WEEKDAY(Q$6,1)=1,WEEKDAY(Q$6,1)=7),0,MIN(8,Q9)*Q8))</f>
+      </c>
+      <c r="R10" s="21">
+        <f>IF(R$6="","",IF(OR(WEEKDAY(R$6,1)=1,WEEKDAY(R$6,1)=7),0,MIN(8,R9)*R8))</f>
+      </c>
+    </row>
+    <row r="11" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B11" s="21">
+        <f>SUM(L11:R11)</f>
+      </c>
+      <c r="D11" s="29">
+        <f>B11*E11</f>
+      </c>
+      <c r="E11" s="29">
+        <f>'Rate Tables'!D10</f>
+      </c>
+      <c r="F11" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="P6" s="7" t="s">
+      <c r="L11" s="21">
+        <f>IF(L$6="","",IF(WEEKDAY(L$6,1)=1,0,IF(WEEKDAY(L$6,1)=7,L9*L8,MAX(0,L9-8)*L8)))</f>
+      </c>
+      <c r="M11" s="21">
+        <f>IF(M$6="","",IF(WEEKDAY(M$6,1)=1,0,IF(WEEKDAY(M$6,1)=7,M9*M8,MAX(0,M9-8)*M8)))</f>
+      </c>
+      <c r="N11" s="21">
+        <f>IF(N$6="","",IF(WEEKDAY(N$6,1)=1,0,IF(WEEKDAY(N$6,1)=7,N9*N8,MAX(0,N9-8)*N8)))</f>
+      </c>
+      <c r="O11" s="21">
+        <f>IF(O$6="","",IF(WEEKDAY(O$6,1)=1,0,IF(WEEKDAY(O$6,1)=7,O9*O8,MAX(0,O9-8)*O8)))</f>
+      </c>
+      <c r="P11" s="21">
+        <f>IF(P$6="","",IF(WEEKDAY(P$6,1)=1,0,IF(WEEKDAY(P$6,1)=7,P9*P8,MAX(0,P9-8)*P8)))</f>
+      </c>
+      <c r="Q11" s="21">
+        <f>IF(Q$6="","",IF(WEEKDAY(Q$6,1)=1,0,IF(WEEKDAY(Q$6,1)=7,Q9*Q8,MAX(0,Q9-8)*Q8)))</f>
+      </c>
+      <c r="R11" s="21">
+        <f>IF(R$6="","",IF(WEEKDAY(R$6,1)=1,0,IF(WEEKDAY(R$6,1)=7,R9*R8,MAX(0,R9-8)*R8)))</f>
+      </c>
+    </row>
+    <row r="12" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B12" s="21">
+        <f>SUM(L12:R12)</f>
+      </c>
+      <c r="D12" s="29">
+        <f>B12*E12</f>
+      </c>
+      <c r="E12" s="29">
+        <f>'Rate Tables'!E10</f>
+      </c>
+      <c r="F12" s="8" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="19">
-        <v>1</v>
-      </c>
-      <c r="C7" s="21">
-        <v>8</v>
-      </c>
-      <c r="D7" s="21">
-        <v>2</v>
-      </c>
-      <c r="E7" s="21">
-        <v>0</v>
-      </c>
-      <c r="F7" s="21">
-        <v>1</v>
-      </c>
-      <c r="G7" s="22">
-        <f>'Rate Tables'!C10</f>
-      </c>
-      <c r="H7" s="22">
-        <f>'Rate Tables'!D10</f>
-      </c>
-      <c r="I7" s="22">
-        <f>'Rate Tables'!E10</f>
-      </c>
-      <c r="J7" s="22">
+      <c r="L12" s="21">
+        <f>IF(L$6="","",IF(WEEKDAY(L$6,1)=1,L9*L8,0))</f>
+      </c>
+      <c r="M12" s="21">
+        <f>IF(M$6="","",IF(WEEKDAY(M$6,1)=1,M9*M8,0))</f>
+      </c>
+      <c r="N12" s="21">
+        <f>IF(N$6="","",IF(WEEKDAY(N$6,1)=1,N9*N8,0))</f>
+      </c>
+      <c r="O12" s="21">
+        <f>IF(O$6="","",IF(WEEKDAY(O$6,1)=1,O9*O8,0))</f>
+      </c>
+      <c r="P12" s="21">
+        <f>IF(P$6="","",IF(WEEKDAY(P$6,1)=1,P9*P8,0))</f>
+      </c>
+      <c r="Q12" s="21">
+        <f>IF(Q$6="","",IF(WEEKDAY(Q$6,1)=1,Q9*Q8,0))</f>
+      </c>
+      <c r="R12" s="21">
+        <f>IF(R$6="","",IF(WEEKDAY(R$6,1)=1,R9*R8,0))</f>
+      </c>
+    </row>
+    <row r="13" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B13" s="21">
+        <f>SUM(L13:R13)</f>
+      </c>
+      <c r="D13" s="29">
+        <f>B13*E13</f>
+      </c>
+      <c r="E13" s="29">
         <v>130</v>
       </c>
-      <c r="K7" s="22">
-        <f>C7*G7</f>
-      </c>
-      <c r="L7" s="22">
-        <f>D7*H7</f>
-      </c>
-      <c r="M7" s="22">
-        <f>E7*I7</f>
-      </c>
-      <c r="N7" s="22">
-        <f>F7*J7</f>
-      </c>
-      <c r="O7" s="22">
-        <f>K7+L7+M7</f>
-      </c>
-      <c r="P7" s="21">
-        <f>C7+D7+E7</f>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" s="14" t="s">
+      <c r="F13" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="L13" s="19">
+        <v>1</v>
+      </c>
+      <c r="M13" s="19">
+        <v>1</v>
+      </c>
+      <c r="N13" s="19">
+        <v>1</v>
+      </c>
+      <c r="O13" s="19">
+        <v>1</v>
+      </c>
+      <c r="P13" s="19">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="19">
+        <v>1</v>
+      </c>
+      <c r="R13" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="15">
-        <f>SUM(C7:C7)</f>
-      </c>
-      <c r="D8" s="15">
-        <f>SUM(D7:D7)</f>
-      </c>
-      <c r="E8" s="15">
-        <f>SUM(E7:E7)</f>
-      </c>
-      <c r="F8" s="15">
-        <f>SUM(F7:F7)</f>
-      </c>
-      <c r="K8" s="18">
-        <f>SUM(K7:K7)</f>
-      </c>
-      <c r="L8" s="18">
-        <f>SUM(L7:L7)</f>
-      </c>
-      <c r="M8" s="18">
-        <f>SUM(M7:M7)</f>
-      </c>
-      <c r="N8" s="18">
-        <f>SUM(N7:N7)</f>
-      </c>
-      <c r="O8" s="18">
-        <f>SUM(O7:O7)</f>
-      </c>
-      <c r="P8" s="15">
-        <f>SUM(P7:P7)</f>
+      <c r="B14" s="15">
+        <f>SUM(B7)</f>
+      </c>
+      <c r="D14" s="18">
+        <f>SUM(D13)</f>
+      </c>
+      <c r="G14" s="15">
+        <f>SUM(G7)</f>
+      </c>
+      <c r="H14" s="15">
+        <f>SUM(H7)</f>
+      </c>
+      <c r="I14" s="15">
+        <f>SUM(I7)</f>
+      </c>
+      <c r="J14" s="15">
+        <f>SUM(J7)</f>
+      </c>
+      <c r="K14" s="18">
+        <f>SUM(K7)</f>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="A3:P3"/>
+    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="A3:R3"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.65" bottom="0.65" header="0.28" footer="0.28"/>
-  <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="20"/>
+  <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;B HIT SQUAD / PROJECT CONTROLS &amp;C Foremen &amp;R Confidential</oddHeader>
     <oddFooter>&amp;L Produced by Hit Squad Project Controls &amp;C &amp;D &amp;R Page &amp;P of &amp;N</oddFooter>
@@ -2741,17 +3471,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF1F8A96"/>
-    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:R28"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="32" customWidth="1"/>
-    <col min="2" max="6" width="12" customWidth="1"/>
-    <col min="7" max="16" width="14" customWidth="1"/>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="26" customWidth="1"/>
+    <col min="4" max="5" width="14" customWidth="1"/>
+    <col min="6" max="10" width="12" customWidth="1"/>
+    <col min="11" max="11" width="14" customWidth="1"/>
+    <col min="12" max="18" width="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" ht="22" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2770,13 +3503,15 @@
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -2795,6 +3530,8 @@
       <c r="N3" s="3"/>
       <c r="O3" s="3"/>
       <c r="P3" s="3"/>
+      <c r="Q3" s="3"/>
+      <c r="R3" s="3"/>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
@@ -2806,202 +3543,771 @@
         <v>4</v>
       </c>
       <c r="B5" s="6">
-        <v>46269.6956406713</v>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+        <v>46269.709873078704</v>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>47</v>
       </c>
       <c r="C6" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="G6" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="H6" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="I6" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="F6" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="I6" s="7" t="s">
+      <c r="J6" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="J6" s="7" t="s">
+      <c r="K6" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="L6" s="22">
+        <v>46266</v>
+      </c>
+      <c r="M6" s="22">
+        <f>L6+1</f>
+      </c>
+      <c r="N6" s="22">
+        <f>M6+1</f>
+      </c>
+      <c r="O6" s="22">
+        <f>N6+1</f>
+      </c>
+      <c r="P6" s="22">
+        <f>O6+1</f>
+      </c>
+      <c r="Q6" s="22">
+        <f>P6+1</f>
+      </c>
+      <c r="R6" s="22">
+        <f>Q6+1</f>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="K6" s="7" t="s">
+      <c r="B7" s="24">
+        <f>G7+H7+I7</f>
+      </c>
+      <c r="C7" s="23" t="s">
+        <v>60</v>
+      </c>
+      <c r="D7" s="25">
+        <f>K7</f>
+      </c>
+      <c r="G7" s="24">
+        <f>B10</f>
+      </c>
+      <c r="H7" s="24">
+        <f>B11</f>
+      </c>
+      <c r="I7" s="24">
+        <f>B12</f>
+      </c>
+      <c r="J7" s="24">
+        <f>B13</f>
+      </c>
+      <c r="K7" s="25">
+        <f>D10+D11+D12</f>
+      </c>
+    </row>
+    <row r="8" spans="6:18" x14ac:dyDescent="0.25">
+      <c r="F8" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="L6" s="7" t="s">
+      <c r="L8" s="27">
+        <v>4</v>
+      </c>
+      <c r="M8" s="27">
+        <v>4</v>
+      </c>
+      <c r="N8" s="27">
+        <v>4</v>
+      </c>
+      <c r="O8" s="27">
+        <v>4</v>
+      </c>
+      <c r="P8" s="27">
+        <v>4</v>
+      </c>
+      <c r="Q8" s="27">
+        <v>4</v>
+      </c>
+      <c r="R8" s="27">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A9" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="M6" s="7" t="s">
+      <c r="F9" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="N6" s="7" t="s">
+      <c r="L9" s="28">
+        <v>10</v>
+      </c>
+      <c r="M9" s="28">
+        <v>10</v>
+      </c>
+      <c r="N9" s="28">
+        <v>10</v>
+      </c>
+      <c r="O9" s="28">
+        <v>10</v>
+      </c>
+      <c r="P9" s="28">
+        <v>10</v>
+      </c>
+      <c r="Q9" s="28">
+        <v>10</v>
+      </c>
+      <c r="R9" s="28">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B10" s="21">
+        <f>SUM(L10:R10)</f>
+      </c>
+      <c r="D10" s="29">
+        <f>B10*E10</f>
+      </c>
+      <c r="E10" s="29">
+        <f>'Rate Tables'!C11</f>
+      </c>
+      <c r="F10" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="O6" s="7" t="s">
+      <c r="L10" s="21">
+        <f>IF(L$6="","",IF(OR(WEEKDAY(L$6,1)=1,WEEKDAY(L$6,1)=7),0,MIN(8,L9)*L8))</f>
+      </c>
+      <c r="M10" s="21">
+        <f>IF(M$6="","",IF(OR(WEEKDAY(M$6,1)=1,WEEKDAY(M$6,1)=7),0,MIN(8,M9)*M8))</f>
+      </c>
+      <c r="N10" s="21">
+        <f>IF(N$6="","",IF(OR(WEEKDAY(N$6,1)=1,WEEKDAY(N$6,1)=7),0,MIN(8,N9)*N8))</f>
+      </c>
+      <c r="O10" s="21">
+        <f>IF(O$6="","",IF(OR(WEEKDAY(O$6,1)=1,WEEKDAY(O$6,1)=7),0,MIN(8,O9)*O8))</f>
+      </c>
+      <c r="P10" s="21">
+        <f>IF(P$6="","",IF(OR(WEEKDAY(P$6,1)=1,WEEKDAY(P$6,1)=7),0,MIN(8,P9)*P8))</f>
+      </c>
+      <c r="Q10" s="21">
+        <f>IF(Q$6="","",IF(OR(WEEKDAY(Q$6,1)=1,WEEKDAY(Q$6,1)=7),0,MIN(8,Q9)*Q8))</f>
+      </c>
+      <c r="R10" s="21">
+        <f>IF(R$6="","",IF(OR(WEEKDAY(R$6,1)=1,WEEKDAY(R$6,1)=7),0,MIN(8,R9)*R8))</f>
+      </c>
+    </row>
+    <row r="11" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B11" s="21">
+        <f>SUM(L11:R11)</f>
+      </c>
+      <c r="D11" s="29">
+        <f>B11*E11</f>
+      </c>
+      <c r="E11" s="29">
+        <f>'Rate Tables'!D11</f>
+      </c>
+      <c r="F11" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="P6" s="7" t="s">
+      <c r="L11" s="21">
+        <f>IF(L$6="","",IF(WEEKDAY(L$6,1)=1,0,IF(WEEKDAY(L$6,1)=7,L9*L8,MAX(0,L9-8)*L8)))</f>
+      </c>
+      <c r="M11" s="21">
+        <f>IF(M$6="","",IF(WEEKDAY(M$6,1)=1,0,IF(WEEKDAY(M$6,1)=7,M9*M8,MAX(0,M9-8)*M8)))</f>
+      </c>
+      <c r="N11" s="21">
+        <f>IF(N$6="","",IF(WEEKDAY(N$6,1)=1,0,IF(WEEKDAY(N$6,1)=7,N9*N8,MAX(0,N9-8)*N8)))</f>
+      </c>
+      <c r="O11" s="21">
+        <f>IF(O$6="","",IF(WEEKDAY(O$6,1)=1,0,IF(WEEKDAY(O$6,1)=7,O9*O8,MAX(0,O9-8)*O8)))</f>
+      </c>
+      <c r="P11" s="21">
+        <f>IF(P$6="","",IF(WEEKDAY(P$6,1)=1,0,IF(WEEKDAY(P$6,1)=7,P9*P8,MAX(0,P9-8)*P8)))</f>
+      </c>
+      <c r="Q11" s="21">
+        <f>IF(Q$6="","",IF(WEEKDAY(Q$6,1)=1,0,IF(WEEKDAY(Q$6,1)=7,Q9*Q8,MAX(0,Q9-8)*Q8)))</f>
+      </c>
+      <c r="R11" s="21">
+        <f>IF(R$6="","",IF(WEEKDAY(R$6,1)=1,0,IF(WEEKDAY(R$6,1)=7,R9*R8,MAX(0,R9-8)*R8)))</f>
+      </c>
+    </row>
+    <row r="12" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B12" s="21">
+        <f>SUM(L12:R12)</f>
+      </c>
+      <c r="D12" s="29">
+        <f>B12*E12</f>
+      </c>
+      <c r="E12" s="29">
+        <f>'Rate Tables'!E11</f>
+      </c>
+      <c r="F12" s="8" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
+      <c r="L12" s="21">
+        <f>IF(L$6="","",IF(WEEKDAY(L$6,1)=1,L9*L8,0))</f>
+      </c>
+      <c r="M12" s="21">
+        <f>IF(M$6="","",IF(WEEKDAY(M$6,1)=1,M9*M8,0))</f>
+      </c>
+      <c r="N12" s="21">
+        <f>IF(N$6="","",IF(WEEKDAY(N$6,1)=1,N9*N8,0))</f>
+      </c>
+      <c r="O12" s="21">
+        <f>IF(O$6="","",IF(WEEKDAY(O$6,1)=1,O9*O8,0))</f>
+      </c>
+      <c r="P12" s="21">
+        <f>IF(P$6="","",IF(WEEKDAY(P$6,1)=1,P9*P8,0))</f>
+      </c>
+      <c r="Q12" s="21">
+        <f>IF(Q$6="","",IF(WEEKDAY(Q$6,1)=1,Q9*Q8,0))</f>
+      </c>
+      <c r="R12" s="21">
+        <f>IF(R$6="","",IF(WEEKDAY(R$6,1)=1,R9*R8,0))</f>
+      </c>
+    </row>
+    <row r="13" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B13" s="21">
+        <f>SUM(L13:R13)</f>
+      </c>
+      <c r="D13" s="29">
+        <f>B13*E13</f>
+      </c>
+      <c r="E13" s="29">
+        <v>130</v>
+      </c>
+      <c r="F13" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="B7" s="19">
+      <c r="L13" s="19">
         <v>4</v>
       </c>
-      <c r="C7" s="21">
-        <v>32</v>
-      </c>
-      <c r="D7" s="21">
-        <v>8</v>
-      </c>
-      <c r="E7" s="21">
+      <c r="M13" s="19">
+        <v>4</v>
+      </c>
+      <c r="N13" s="19">
+        <v>4</v>
+      </c>
+      <c r="O13" s="19">
+        <v>4</v>
+      </c>
+      <c r="P13" s="19">
+        <v>4</v>
+      </c>
+      <c r="Q13" s="19">
+        <v>4</v>
+      </c>
+      <c r="R13" s="19">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="B14" s="24">
+        <f>G14+H14+I14</f>
+      </c>
+      <c r="C14" s="23" t="s">
+        <v>60</v>
+      </c>
+      <c r="D14" s="25">
+        <f>K14</f>
+      </c>
+      <c r="G14" s="24">
+        <f>B17</f>
+      </c>
+      <c r="H14" s="24">
+        <f>B18</f>
+      </c>
+      <c r="I14" s="24">
+        <f>B19</f>
+      </c>
+      <c r="J14" s="24">
+        <f>B20</f>
+      </c>
+      <c r="K14" s="25">
+        <f>D17+D18+D19</f>
+      </c>
+    </row>
+    <row r="15" spans="6:18" x14ac:dyDescent="0.25">
+      <c r="F15" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="L15" s="27">
+        <v>2</v>
+      </c>
+      <c r="M15" s="27">
+        <v>2</v>
+      </c>
+      <c r="N15" s="27">
+        <v>2</v>
+      </c>
+      <c r="O15" s="27">
+        <v>2</v>
+      </c>
+      <c r="P15" s="27">
+        <v>2</v>
+      </c>
+      <c r="Q15" s="27">
+        <v>2</v>
+      </c>
+      <c r="R15" s="27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A16" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="F16" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="L16" s="28">
+        <v>10</v>
+      </c>
+      <c r="M16" s="28">
+        <v>10</v>
+      </c>
+      <c r="N16" s="28">
+        <v>10</v>
+      </c>
+      <c r="O16" s="28">
+        <v>10</v>
+      </c>
+      <c r="P16" s="28">
+        <v>10</v>
+      </c>
+      <c r="Q16" s="28">
+        <v>10</v>
+      </c>
+      <c r="R16" s="28">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B17" s="21">
+        <f>SUM(L17:R17)</f>
+      </c>
+      <c r="D17" s="29">
+        <f>B17*E17</f>
+      </c>
+      <c r="E17" s="29">
+        <f>'Rate Tables'!C11</f>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="L17" s="21">
+        <f>IF(L$6="","",IF(OR(WEEKDAY(L$6,1)=1,WEEKDAY(L$6,1)=7),0,MIN(8,L16)*L15))</f>
+      </c>
+      <c r="M17" s="21">
+        <f>IF(M$6="","",IF(OR(WEEKDAY(M$6,1)=1,WEEKDAY(M$6,1)=7),0,MIN(8,M16)*M15))</f>
+      </c>
+      <c r="N17" s="21">
+        <f>IF(N$6="","",IF(OR(WEEKDAY(N$6,1)=1,WEEKDAY(N$6,1)=7),0,MIN(8,N16)*N15))</f>
+      </c>
+      <c r="O17" s="21">
+        <f>IF(O$6="","",IF(OR(WEEKDAY(O$6,1)=1,WEEKDAY(O$6,1)=7),0,MIN(8,O16)*O15))</f>
+      </c>
+      <c r="P17" s="21">
+        <f>IF(P$6="","",IF(OR(WEEKDAY(P$6,1)=1,WEEKDAY(P$6,1)=7),0,MIN(8,P16)*P15))</f>
+      </c>
+      <c r="Q17" s="21">
+        <f>IF(Q$6="","",IF(OR(WEEKDAY(Q$6,1)=1,WEEKDAY(Q$6,1)=7),0,MIN(8,Q16)*Q15))</f>
+      </c>
+      <c r="R17" s="21">
+        <f>IF(R$6="","",IF(OR(WEEKDAY(R$6,1)=1,WEEKDAY(R$6,1)=7),0,MIN(8,R16)*R15))</f>
+      </c>
+    </row>
+    <row r="18" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B18" s="21">
+        <f>SUM(L18:R18)</f>
+      </c>
+      <c r="D18" s="29">
+        <f>B18*E18</f>
+      </c>
+      <c r="E18" s="29">
+        <f>'Rate Tables'!D11</f>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="L18" s="21">
+        <f>IF(L$6="","",IF(WEEKDAY(L$6,1)=1,0,IF(WEEKDAY(L$6,1)=7,L16*L15,MAX(0,L16-8)*L15)))</f>
+      </c>
+      <c r="M18" s="21">
+        <f>IF(M$6="","",IF(WEEKDAY(M$6,1)=1,0,IF(WEEKDAY(M$6,1)=7,M16*M15,MAX(0,M16-8)*M15)))</f>
+      </c>
+      <c r="N18" s="21">
+        <f>IF(N$6="","",IF(WEEKDAY(N$6,1)=1,0,IF(WEEKDAY(N$6,1)=7,N16*N15,MAX(0,N16-8)*N15)))</f>
+      </c>
+      <c r="O18" s="21">
+        <f>IF(O$6="","",IF(WEEKDAY(O$6,1)=1,0,IF(WEEKDAY(O$6,1)=7,O16*O15,MAX(0,O16-8)*O15)))</f>
+      </c>
+      <c r="P18" s="21">
+        <f>IF(P$6="","",IF(WEEKDAY(P$6,1)=1,0,IF(WEEKDAY(P$6,1)=7,P16*P15,MAX(0,P16-8)*P15)))</f>
+      </c>
+      <c r="Q18" s="21">
+        <f>IF(Q$6="","",IF(WEEKDAY(Q$6,1)=1,0,IF(WEEKDAY(Q$6,1)=7,Q16*Q15,MAX(0,Q16-8)*Q15)))</f>
+      </c>
+      <c r="R18" s="21">
+        <f>IF(R$6="","",IF(WEEKDAY(R$6,1)=1,0,IF(WEEKDAY(R$6,1)=7,R16*R15,MAX(0,R16-8)*R15)))</f>
+      </c>
+    </row>
+    <row r="19" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B19" s="21">
+        <f>SUM(L19:R19)</f>
+      </c>
+      <c r="D19" s="29">
+        <f>B19*E19</f>
+      </c>
+      <c r="E19" s="29">
+        <f>'Rate Tables'!E11</f>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="L19" s="21">
+        <f>IF(L$6="","",IF(WEEKDAY(L$6,1)=1,L16*L15,0))</f>
+      </c>
+      <c r="M19" s="21">
+        <f>IF(M$6="","",IF(WEEKDAY(M$6,1)=1,M16*M15,0))</f>
+      </c>
+      <c r="N19" s="21">
+        <f>IF(N$6="","",IF(WEEKDAY(N$6,1)=1,N16*N15,0))</f>
+      </c>
+      <c r="O19" s="21">
+        <f>IF(O$6="","",IF(WEEKDAY(O$6,1)=1,O16*O15,0))</f>
+      </c>
+      <c r="P19" s="21">
+        <f>IF(P$6="","",IF(WEEKDAY(P$6,1)=1,P16*P15,0))</f>
+      </c>
+      <c r="Q19" s="21">
+        <f>IF(Q$6="","",IF(WEEKDAY(Q$6,1)=1,Q16*Q15,0))</f>
+      </c>
+      <c r="R19" s="21">
+        <f>IF(R$6="","",IF(WEEKDAY(R$6,1)=1,R16*R15,0))</f>
+      </c>
+    </row>
+    <row r="20" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B20" s="21">
+        <f>SUM(L20:R20)</f>
+      </c>
+      <c r="D20" s="29">
+        <f>B20*E20</f>
+      </c>
+      <c r="E20" s="29">
+        <v>130</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="L20" s="19">
         <v>0</v>
       </c>
-      <c r="F7" s="21">
-        <v>4</v>
-      </c>
-      <c r="G7" s="22">
-        <f>'Rate Tables'!C11</f>
-      </c>
-      <c r="H7" s="22">
-        <f>'Rate Tables'!D11</f>
-      </c>
-      <c r="I7" s="22">
-        <f>'Rate Tables'!E11</f>
-      </c>
-      <c r="J7" s="22">
+      <c r="M20" s="19">
+        <v>0</v>
+      </c>
+      <c r="N20" s="19">
+        <v>0</v>
+      </c>
+      <c r="O20" s="19">
+        <v>0</v>
+      </c>
+      <c r="P20" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="19">
+        <v>0</v>
+      </c>
+      <c r="R20" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="B21" s="24">
+        <f>G21+H21+I21</f>
+      </c>
+      <c r="C21" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="D21" s="25">
+        <f>K21</f>
+      </c>
+      <c r="G21" s="24">
+        <f>B24</f>
+      </c>
+      <c r="H21" s="24">
+        <f>B25</f>
+      </c>
+      <c r="I21" s="24">
+        <f>B26</f>
+      </c>
+      <c r="J21" s="24">
+        <f>B27</f>
+      </c>
+      <c r="K21" s="25">
+        <f>D24+D25+D26</f>
+      </c>
+    </row>
+    <row r="22" spans="6:18" x14ac:dyDescent="0.25">
+      <c r="F22" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="L22" s="27">
+        <v>3</v>
+      </c>
+      <c r="M22" s="27">
+        <v>3</v>
+      </c>
+      <c r="N22" s="27">
+        <v>3</v>
+      </c>
+      <c r="O22" s="27">
+        <v>3</v>
+      </c>
+      <c r="P22" s="27">
+        <v>3</v>
+      </c>
+      <c r="Q22" s="27">
+        <v>3</v>
+      </c>
+      <c r="R22" s="27">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A23" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="F23" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="L23" s="28">
+        <v>10</v>
+      </c>
+      <c r="M23" s="28">
+        <v>10</v>
+      </c>
+      <c r="N23" s="28">
+        <v>10</v>
+      </c>
+      <c r="O23" s="28">
+        <v>10</v>
+      </c>
+      <c r="P23" s="28">
+        <v>10</v>
+      </c>
+      <c r="Q23" s="28">
+        <v>10</v>
+      </c>
+      <c r="R23" s="28">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B24" s="21">
+        <f>SUM(L24:R24)</f>
+      </c>
+      <c r="D24" s="29">
+        <f>B24*E24</f>
+      </c>
+      <c r="E24" s="29">
+        <f>'Rate Tables'!C12</f>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="L24" s="21">
+        <f>IF(L$6="","",IF(OR(WEEKDAY(L$6,1)=1,WEEKDAY(L$6,1)=7),0,MIN(8,L23)*L22))</f>
+      </c>
+      <c r="M24" s="21">
+        <f>IF(M$6="","",IF(OR(WEEKDAY(M$6,1)=1,WEEKDAY(M$6,1)=7),0,MIN(8,M23)*M22))</f>
+      </c>
+      <c r="N24" s="21">
+        <f>IF(N$6="","",IF(OR(WEEKDAY(N$6,1)=1,WEEKDAY(N$6,1)=7),0,MIN(8,N23)*N22))</f>
+      </c>
+      <c r="O24" s="21">
+        <f>IF(O$6="","",IF(OR(WEEKDAY(O$6,1)=1,WEEKDAY(O$6,1)=7),0,MIN(8,O23)*O22))</f>
+      </c>
+      <c r="P24" s="21">
+        <f>IF(P$6="","",IF(OR(WEEKDAY(P$6,1)=1,WEEKDAY(P$6,1)=7),0,MIN(8,P23)*P22))</f>
+      </c>
+      <c r="Q24" s="21">
+        <f>IF(Q$6="","",IF(OR(WEEKDAY(Q$6,1)=1,WEEKDAY(Q$6,1)=7),0,MIN(8,Q23)*Q22))</f>
+      </c>
+      <c r="R24" s="21">
+        <f>IF(R$6="","",IF(OR(WEEKDAY(R$6,1)=1,WEEKDAY(R$6,1)=7),0,MIN(8,R23)*R22))</f>
+      </c>
+    </row>
+    <row r="25" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B25" s="21">
+        <f>SUM(L25:R25)</f>
+      </c>
+      <c r="D25" s="29">
+        <f>B25*E25</f>
+      </c>
+      <c r="E25" s="29">
+        <f>'Rate Tables'!D12</f>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="L25" s="21">
+        <f>IF(L$6="","",IF(WEEKDAY(L$6,1)=1,0,IF(WEEKDAY(L$6,1)=7,L23*L22,MAX(0,L23-8)*L22)))</f>
+      </c>
+      <c r="M25" s="21">
+        <f>IF(M$6="","",IF(WEEKDAY(M$6,1)=1,0,IF(WEEKDAY(M$6,1)=7,M23*M22,MAX(0,M23-8)*M22)))</f>
+      </c>
+      <c r="N25" s="21">
+        <f>IF(N$6="","",IF(WEEKDAY(N$6,1)=1,0,IF(WEEKDAY(N$6,1)=7,N23*N22,MAX(0,N23-8)*N22)))</f>
+      </c>
+      <c r="O25" s="21">
+        <f>IF(O$6="","",IF(WEEKDAY(O$6,1)=1,0,IF(WEEKDAY(O$6,1)=7,O23*O22,MAX(0,O23-8)*O22)))</f>
+      </c>
+      <c r="P25" s="21">
+        <f>IF(P$6="","",IF(WEEKDAY(P$6,1)=1,0,IF(WEEKDAY(P$6,1)=7,P23*P22,MAX(0,P23-8)*P22)))</f>
+      </c>
+      <c r="Q25" s="21">
+        <f>IF(Q$6="","",IF(WEEKDAY(Q$6,1)=1,0,IF(WEEKDAY(Q$6,1)=7,Q23*Q22,MAX(0,Q23-8)*Q22)))</f>
+      </c>
+      <c r="R25" s="21">
+        <f>IF(R$6="","",IF(WEEKDAY(R$6,1)=1,0,IF(WEEKDAY(R$6,1)=7,R23*R22,MAX(0,R23-8)*R22)))</f>
+      </c>
+    </row>
+    <row r="26" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B26" s="21">
+        <f>SUM(L26:R26)</f>
+      </c>
+      <c r="D26" s="29">
+        <f>B26*E26</f>
+      </c>
+      <c r="E26" s="29">
+        <f>'Rate Tables'!E12</f>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="L26" s="21">
+        <f>IF(L$6="","",IF(WEEKDAY(L$6,1)=1,L23*L22,0))</f>
+      </c>
+      <c r="M26" s="21">
+        <f>IF(M$6="","",IF(WEEKDAY(M$6,1)=1,M23*M22,0))</f>
+      </c>
+      <c r="N26" s="21">
+        <f>IF(N$6="","",IF(WEEKDAY(N$6,1)=1,N23*N22,0))</f>
+      </c>
+      <c r="O26" s="21">
+        <f>IF(O$6="","",IF(WEEKDAY(O$6,1)=1,O23*O22,0))</f>
+      </c>
+      <c r="P26" s="21">
+        <f>IF(P$6="","",IF(WEEKDAY(P$6,1)=1,P23*P22,0))</f>
+      </c>
+      <c r="Q26" s="21">
+        <f>IF(Q$6="","",IF(WEEKDAY(Q$6,1)=1,Q23*Q22,0))</f>
+      </c>
+      <c r="R26" s="21">
+        <f>IF(R$6="","",IF(WEEKDAY(R$6,1)=1,R23*R22,0))</f>
+      </c>
+    </row>
+    <row r="27" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B27" s="21">
+        <f>SUM(L27:R27)</f>
+      </c>
+      <c r="D27" s="29">
+        <f>B27*E27</f>
+      </c>
+      <c r="E27" s="29">
         <v>130</v>
       </c>
-      <c r="K7" s="22">
-        <f>C7*G7</f>
-      </c>
-      <c r="L7" s="22">
-        <f>D7*H7</f>
-      </c>
-      <c r="M7" s="22">
-        <f>E7*I7</f>
-      </c>
-      <c r="N7" s="22">
-        <f>F7*J7</f>
-      </c>
-      <c r="O7" s="22">
-        <f>K7+L7+M7</f>
-      </c>
-      <c r="P7" s="21">
-        <f>C7+D7+E7</f>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="B8" s="20">
+      <c r="F27" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="L27" s="19">
         <v>3</v>
       </c>
-      <c r="C8" s="23">
-        <v>24</v>
-      </c>
-      <c r="D8" s="23">
-        <v>6</v>
-      </c>
-      <c r="E8" s="23">
-        <v>0</v>
-      </c>
-      <c r="F8" s="23">
+      <c r="M27" s="19">
         <v>3</v>
       </c>
-      <c r="G8" s="24">
-        <f>'Rate Tables'!C12</f>
-      </c>
-      <c r="H8" s="24">
-        <f>'Rate Tables'!D12</f>
-      </c>
-      <c r="I8" s="24">
-        <f>'Rate Tables'!E12</f>
-      </c>
-      <c r="J8" s="24">
-        <v>130</v>
-      </c>
-      <c r="K8" s="24">
-        <f>C8*G8</f>
-      </c>
-      <c r="L8" s="24">
-        <f>D8*H8</f>
-      </c>
-      <c r="M8" s="24">
-        <f>E8*I8</f>
-      </c>
-      <c r="N8" s="24">
-        <f>F8*J8</f>
-      </c>
-      <c r="O8" s="24">
-        <f>K8+L8+M8</f>
-      </c>
-      <c r="P8" s="23">
-        <f>C8+D8+E8</f>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" s="14" t="s">
+      <c r="N27" s="19">
+        <v>3</v>
+      </c>
+      <c r="O27" s="19">
+        <v>3</v>
+      </c>
+      <c r="P27" s="19">
+        <v>3</v>
+      </c>
+      <c r="Q27" s="19">
+        <v>3</v>
+      </c>
+      <c r="R27" s="19">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="C9" s="15">
-        <f>SUM(C7:C8)</f>
-      </c>
-      <c r="D9" s="15">
-        <f>SUM(D7:D8)</f>
-      </c>
-      <c r="E9" s="15">
-        <f>SUM(E7:E8)</f>
-      </c>
-      <c r="F9" s="15">
-        <f>SUM(F7:F8)</f>
-      </c>
-      <c r="K9" s="18">
-        <f>SUM(K7:K8)</f>
-      </c>
-      <c r="L9" s="18">
-        <f>SUM(L7:L8)</f>
-      </c>
-      <c r="M9" s="18">
-        <f>SUM(M7:M8)</f>
-      </c>
-      <c r="N9" s="18">
-        <f>SUM(N7:N8)</f>
-      </c>
-      <c r="O9" s="18">
-        <f>SUM(O7:O8)</f>
-      </c>
-      <c r="P9" s="15">
-        <f>SUM(P7:P8)</f>
+      <c r="B28" s="15">
+        <f>SUM(B7,B14,B21)</f>
+      </c>
+      <c r="D28" s="18">
+        <f>SUM(D13,D20,D27)</f>
+      </c>
+      <c r="G28" s="15">
+        <f>SUM(G7,G14,G21)</f>
+      </c>
+      <c r="H28" s="15">
+        <f>SUM(H7,H14,H21)</f>
+      </c>
+      <c r="I28" s="15">
+        <f>SUM(I7,I14,I21)</f>
+      </c>
+      <c r="J28" s="15">
+        <f>SUM(J7,J14,J21)</f>
+      </c>
+      <c r="K28" s="18">
+        <f>SUM(K7,K14,K21)</f>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="A3:P3"/>
+    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="A3:R3"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.65" bottom="0.65" header="0.28" footer="0.28"/>
-  <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="20"/>
+  <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;B HIT SQUAD / PROJECT CONTROLS &amp;C Direct &amp;R Confidential</oddHeader>
     <oddFooter>&amp;L Produced by Hit Squad Project Controls &amp;C &amp;D &amp;R Page &amp;P of &amp;N</oddFooter>
@@ -3015,17 +4321,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF1F8A96"/>
-    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P8"/>
+  <dimension ref="A1:R14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="32" customWidth="1"/>
-    <col min="2" max="6" width="12" customWidth="1"/>
-    <col min="7" max="16" width="14" customWidth="1"/>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="26" customWidth="1"/>
+    <col min="4" max="5" width="14" customWidth="1"/>
+    <col min="6" max="10" width="12" customWidth="1"/>
+    <col min="11" max="11" width="14" customWidth="1"/>
+    <col min="12" max="18" width="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" ht="22" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3044,13 +4353,15 @@
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -3069,6 +4380,8 @@
       <c r="N3" s="3"/>
       <c r="O3" s="3"/>
       <c r="P3" s="3"/>
+      <c r="Q3" s="3"/>
+      <c r="R3" s="3"/>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
@@ -3080,152 +4393,323 @@
         <v>4</v>
       </c>
       <c r="B5" s="6">
-        <v>46269.69564068287</v>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+        <v>46269.70987310185</v>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>47</v>
       </c>
       <c r="C6" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="G6" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="H6" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="I6" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="F6" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="I6" s="7" t="s">
+      <c r="J6" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="J6" s="7" t="s">
+      <c r="K6" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="L6" s="22">
+        <v>46266</v>
+      </c>
+      <c r="M6" s="22">
+        <f>L6+1</f>
+      </c>
+      <c r="N6" s="22">
+        <f>M6+1</f>
+      </c>
+      <c r="O6" s="22">
+        <f>N6+1</f>
+      </c>
+      <c r="P6" s="22">
+        <f>O6+1</f>
+      </c>
+      <c r="Q6" s="22">
+        <f>P6+1</f>
+      </c>
+      <c r="R6" s="22">
+        <f>Q6+1</f>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="K6" s="7" t="s">
+      <c r="B7" s="24">
+        <f>G7+H7+I7</f>
+      </c>
+      <c r="C7" s="23" t="s">
+        <v>63</v>
+      </c>
+      <c r="D7" s="25">
+        <f>K7</f>
+      </c>
+      <c r="G7" s="24">
+        <f>B10</f>
+      </c>
+      <c r="H7" s="24">
+        <f>B11</f>
+      </c>
+      <c r="I7" s="24">
+        <f>B12</f>
+      </c>
+      <c r="J7" s="24">
+        <f>B13</f>
+      </c>
+      <c r="K7" s="25">
+        <f>D10+D11+D12</f>
+      </c>
+    </row>
+    <row r="8" spans="6:18" x14ac:dyDescent="0.25">
+      <c r="F8" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="L6" s="7" t="s">
+      <c r="L8" s="27">
+        <v>1</v>
+      </c>
+      <c r="M8" s="27">
+        <v>1</v>
+      </c>
+      <c r="N8" s="27">
+        <v>1</v>
+      </c>
+      <c r="O8" s="27">
+        <v>1</v>
+      </c>
+      <c r="P8" s="27">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="27">
+        <v>1</v>
+      </c>
+      <c r="R8" s="27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A9" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="M6" s="7" t="s">
+      <c r="F9" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="N6" s="7" t="s">
+      <c r="L9" s="28">
+        <v>10</v>
+      </c>
+      <c r="M9" s="28">
+        <v>10</v>
+      </c>
+      <c r="N9" s="28">
+        <v>10</v>
+      </c>
+      <c r="O9" s="28">
+        <v>10</v>
+      </c>
+      <c r="P9" s="28">
+        <v>10</v>
+      </c>
+      <c r="Q9" s="28">
+        <v>10</v>
+      </c>
+      <c r="R9" s="28">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B10" s="21">
+        <f>SUM(L10:R10)</f>
+      </c>
+      <c r="D10" s="29">
+        <f>B10*E10</f>
+      </c>
+      <c r="E10" s="29">
+        <f>'Rate Tables'!C11</f>
+      </c>
+      <c r="F10" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="O6" s="7" t="s">
+      <c r="L10" s="21">
+        <f>IF(L$6="","",IF(OR(WEEKDAY(L$6,1)=1,WEEKDAY(L$6,1)=7),0,MIN(8,L9)*L8))</f>
+      </c>
+      <c r="M10" s="21">
+        <f>IF(M$6="","",IF(OR(WEEKDAY(M$6,1)=1,WEEKDAY(M$6,1)=7),0,MIN(8,M9)*M8))</f>
+      </c>
+      <c r="N10" s="21">
+        <f>IF(N$6="","",IF(OR(WEEKDAY(N$6,1)=1,WEEKDAY(N$6,1)=7),0,MIN(8,N9)*N8))</f>
+      </c>
+      <c r="O10" s="21">
+        <f>IF(O$6="","",IF(OR(WEEKDAY(O$6,1)=1,WEEKDAY(O$6,1)=7),0,MIN(8,O9)*O8))</f>
+      </c>
+      <c r="P10" s="21">
+        <f>IF(P$6="","",IF(OR(WEEKDAY(P$6,1)=1,WEEKDAY(P$6,1)=7),0,MIN(8,P9)*P8))</f>
+      </c>
+      <c r="Q10" s="21">
+        <f>IF(Q$6="","",IF(OR(WEEKDAY(Q$6,1)=1,WEEKDAY(Q$6,1)=7),0,MIN(8,Q9)*Q8))</f>
+      </c>
+      <c r="R10" s="21">
+        <f>IF(R$6="","",IF(OR(WEEKDAY(R$6,1)=1,WEEKDAY(R$6,1)=7),0,MIN(8,R9)*R8))</f>
+      </c>
+    </row>
+    <row r="11" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B11" s="21">
+        <f>SUM(L11:R11)</f>
+      </c>
+      <c r="D11" s="29">
+        <f>B11*E11</f>
+      </c>
+      <c r="E11" s="29">
+        <f>'Rate Tables'!D11</f>
+      </c>
+      <c r="F11" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="P6" s="7" t="s">
+      <c r="L11" s="21">
+        <f>IF(L$6="","",IF(WEEKDAY(L$6,1)=1,0,IF(WEEKDAY(L$6,1)=7,L9*L8,MAX(0,L9-8)*L8)))</f>
+      </c>
+      <c r="M11" s="21">
+        <f>IF(M$6="","",IF(WEEKDAY(M$6,1)=1,0,IF(WEEKDAY(M$6,1)=7,M9*M8,MAX(0,M9-8)*M8)))</f>
+      </c>
+      <c r="N11" s="21">
+        <f>IF(N$6="","",IF(WEEKDAY(N$6,1)=1,0,IF(WEEKDAY(N$6,1)=7,N9*N8,MAX(0,N9-8)*N8)))</f>
+      </c>
+      <c r="O11" s="21">
+        <f>IF(O$6="","",IF(WEEKDAY(O$6,1)=1,0,IF(WEEKDAY(O$6,1)=7,O9*O8,MAX(0,O9-8)*O8)))</f>
+      </c>
+      <c r="P11" s="21">
+        <f>IF(P$6="","",IF(WEEKDAY(P$6,1)=1,0,IF(WEEKDAY(P$6,1)=7,P9*P8,MAX(0,P9-8)*P8)))</f>
+      </c>
+      <c r="Q11" s="21">
+        <f>IF(Q$6="","",IF(WEEKDAY(Q$6,1)=1,0,IF(WEEKDAY(Q$6,1)=7,Q9*Q8,MAX(0,Q9-8)*Q8)))</f>
+      </c>
+      <c r="R11" s="21">
+        <f>IF(R$6="","",IF(WEEKDAY(R$6,1)=1,0,IF(WEEKDAY(R$6,1)=7,R9*R8,MAX(0,R9-8)*R8)))</f>
+      </c>
+    </row>
+    <row r="12" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B12" s="21">
+        <f>SUM(L12:R12)</f>
+      </c>
+      <c r="D12" s="29">
+        <f>B12*E12</f>
+      </c>
+      <c r="E12" s="29">
+        <f>'Rate Tables'!E11</f>
+      </c>
+      <c r="F12" s="8" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="B7" s="19">
-        <v>1</v>
-      </c>
-      <c r="C7" s="21">
-        <v>8</v>
-      </c>
-      <c r="D7" s="21">
-        <v>2</v>
-      </c>
-      <c r="E7" s="21">
-        <v>0</v>
-      </c>
-      <c r="F7" s="21">
-        <v>1</v>
-      </c>
-      <c r="G7" s="22">
-        <f>'Rate Tables'!C11</f>
-      </c>
-      <c r="H7" s="22">
-        <f>'Rate Tables'!D11</f>
-      </c>
-      <c r="I7" s="22">
-        <f>'Rate Tables'!E11</f>
-      </c>
-      <c r="J7" s="22">
+      <c r="L12" s="21">
+        <f>IF(L$6="","",IF(WEEKDAY(L$6,1)=1,L9*L8,0))</f>
+      </c>
+      <c r="M12" s="21">
+        <f>IF(M$6="","",IF(WEEKDAY(M$6,1)=1,M9*M8,0))</f>
+      </c>
+      <c r="N12" s="21">
+        <f>IF(N$6="","",IF(WEEKDAY(N$6,1)=1,N9*N8,0))</f>
+      </c>
+      <c r="O12" s="21">
+        <f>IF(O$6="","",IF(WEEKDAY(O$6,1)=1,O9*O8,0))</f>
+      </c>
+      <c r="P12" s="21">
+        <f>IF(P$6="","",IF(WEEKDAY(P$6,1)=1,P9*P8,0))</f>
+      </c>
+      <c r="Q12" s="21">
+        <f>IF(Q$6="","",IF(WEEKDAY(Q$6,1)=1,Q9*Q8,0))</f>
+      </c>
+      <c r="R12" s="21">
+        <f>IF(R$6="","",IF(WEEKDAY(R$6,1)=1,R9*R8,0))</f>
+      </c>
+    </row>
+    <row r="13" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B13" s="21">
+        <f>SUM(L13:R13)</f>
+      </c>
+      <c r="D13" s="29">
+        <f>B13*E13</f>
+      </c>
+      <c r="E13" s="29">
         <v>130</v>
       </c>
-      <c r="K7" s="22">
-        <f>C7*G7</f>
-      </c>
-      <c r="L7" s="22">
-        <f>D7*H7</f>
-      </c>
-      <c r="M7" s="22">
-        <f>E7*I7</f>
-      </c>
-      <c r="N7" s="22">
-        <f>F7*J7</f>
-      </c>
-      <c r="O7" s="22">
-        <f>K7+L7+M7</f>
-      </c>
-      <c r="P7" s="21">
-        <f>C7+D7+E7</f>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" s="14" t="s">
+      <c r="F13" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="L13" s="19">
+        <v>1</v>
+      </c>
+      <c r="M13" s="19">
+        <v>1</v>
+      </c>
+      <c r="N13" s="19">
+        <v>1</v>
+      </c>
+      <c r="O13" s="19">
+        <v>1</v>
+      </c>
+      <c r="P13" s="19">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="19">
+        <v>1</v>
+      </c>
+      <c r="R13" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="15">
-        <f>SUM(C7:C7)</f>
-      </c>
-      <c r="D8" s="15">
-        <f>SUM(D7:D7)</f>
-      </c>
-      <c r="E8" s="15">
-        <f>SUM(E7:E7)</f>
-      </c>
-      <c r="F8" s="15">
-        <f>SUM(F7:F7)</f>
-      </c>
-      <c r="K8" s="18">
-        <f>SUM(K7:K7)</f>
-      </c>
-      <c r="L8" s="18">
-        <f>SUM(L7:L7)</f>
-      </c>
-      <c r="M8" s="18">
-        <f>SUM(M7:M7)</f>
-      </c>
-      <c r="N8" s="18">
-        <f>SUM(N7:N7)</f>
-      </c>
-      <c r="O8" s="18">
-        <f>SUM(O7:O7)</f>
-      </c>
-      <c r="P8" s="15">
-        <f>SUM(P7:P7)</f>
+      <c r="B14" s="15">
+        <f>SUM(B7)</f>
+      </c>
+      <c r="D14" s="18">
+        <f>SUM(D13)</f>
+      </c>
+      <c r="G14" s="15">
+        <f>SUM(G7)</f>
+      </c>
+      <c r="H14" s="15">
+        <f>SUM(H7)</f>
+      </c>
+      <c r="I14" s="15">
+        <f>SUM(I7)</f>
+      </c>
+      <c r="J14" s="15">
+        <f>SUM(J7)</f>
+      </c>
+      <c r="K14" s="18">
+        <f>SUM(K7)</f>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="A3:P3"/>
+    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="A3:R3"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.65" bottom="0.65" header="0.28" footer="0.28"/>
-  <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="20"/>
+  <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;B HIT SQUAD / PROJECT CONTROLS &amp;C Support &amp;R Confidential</oddHeader>
     <oddFooter>&amp;L Produced by Hit Squad Project Controls &amp;C &amp;D &amp;R Page &amp;P of &amp;N</oddFooter>
@@ -3288,58 +4772,58 @@
         <v>4</v>
       </c>
       <c r="B5" s="6">
-        <v>46269.69564070602</v>
+        <v>46269.709873125</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C7" s="19">
         <v>1</v>
       </c>
       <c r="D7" s="19">
-        <v>1</v>
-      </c>
-      <c r="E7" s="22">
+        <v>7</v>
+      </c>
+      <c r="E7" s="29">
         <v>134</v>
       </c>
-      <c r="F7" s="22">
+      <c r="F7" s="29">
         <v>0</v>
       </c>
-      <c r="G7" s="22">
+      <c r="G7" s="29">
         <f>C7*D7*E7+F7</f>
       </c>
-      <c r="H7" s="22">
+      <c r="H7" s="29">
         <f>G7*1.06</f>
       </c>
     </row>
@@ -3424,58 +4908,58 @@
         <v>4</v>
       </c>
       <c r="B5" s="6">
-        <v>46269.69564070602</v>
+        <v>46269.709873125</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C7" s="19">
         <v>1</v>
       </c>
       <c r="D7" s="19">
-        <v>1</v>
-      </c>
-      <c r="E7" s="22">
+        <v>7</v>
+      </c>
+      <c r="E7" s="29">
         <v>80</v>
       </c>
-      <c r="F7" s="22">
+      <c r="F7" s="29">
         <v>0</v>
       </c>
-      <c r="G7" s="22">
+      <c r="G7" s="29">
         <f>C7*D7*E7+F7</f>
       </c>
-      <c r="H7" s="22">
+      <c r="H7" s="29">
         <f>G7*1.06</f>
       </c>
     </row>

--- a/look-samples/v151_cat2_wood_river_client_package.xlsx
+++ b/look-samples/v151_cat2_wood_river_client_package.xlsx
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="108">
   <si>
     <t>HIT SQUAD / PROJECT CONTROLS</t>
   </si>
@@ -221,6 +221,12 @@
     <t>DAYSHIFT</t>
   </si>
   <si>
+    <t>TITLE</t>
+  </si>
+  <si>
+    <t>st-1|day</t>
+  </si>
+  <si>
     <t>HC</t>
   </si>
   <si>
@@ -242,16 +248,37 @@
     <t>PD</t>
   </si>
   <si>
+    <t>st-2|day</t>
+  </si>
+  <si>
+    <t>gf-1|day</t>
+  </si>
+  <si>
+    <t>fm-1|day</t>
+  </si>
+  <si>
     <t>Boilermaker Journeyman</t>
   </si>
   <si>
+    <t>dr-1|day</t>
+  </si>
+  <si>
     <t>NIGHTSHIFT</t>
   </si>
   <si>
+    <t>dr-1|night</t>
+  </si>
+  <si>
     <t>Pipefitter Journeyman</t>
   </si>
   <si>
+    <t>dr-2|day</t>
+  </si>
+  <si>
     <t>Fire Watch</t>
+  </si>
+  <si>
+    <t>su-1|day</t>
   </si>
   <si>
     <t>Item</t>
@@ -922,7 +949,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="6">
-        <v>46269.70987314815</v>
+        <v>46269.71298548611</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1153,41 +1180,41 @@
         <v>4</v>
       </c>
       <c r="B5" s="6">
-        <v>46269.709873125</v>
+        <v>46269.71298545139</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="C7" s="19">
         <v>1</v>
@@ -1292,41 +1319,41 @@
         <v>4</v>
       </c>
       <c r="B5" s="6">
-        <v>46269.70987314815</v>
+        <v>46269.712985474536</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="B6" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D6" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C6" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>68</v>
-      </c>
       <c r="E6" s="7" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="C7" s="19">
         <v>1</v>
@@ -1335,7 +1362,7 @@
         <v>500</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="F7" s="29">
         <f>C7*D7</f>
@@ -1429,38 +1456,38 @@
         <v>4</v>
       </c>
       <c r="B5" s="6">
-        <v>46269.70987313657</v>
+        <v>46269.71298546296</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="C7" s="19">
         <v>1</v>
@@ -1550,29 +1577,29 @@
         <v>4</v>
       </c>
       <c r="B5" s="6">
-        <v>46269.70987314815</v>
+        <v>46269.712985474536</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="B7" s="19">
         <v>3</v>
@@ -1660,32 +1687,32 @@
         <v>4</v>
       </c>
       <c r="B5" s="6">
-        <v>46269.70987314815</v>
+        <v>46269.712985474536</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="C7" s="19">
         <v>1</v>
@@ -1770,27 +1797,27 @@
         <v>4</v>
       </c>
       <c r="B5" s="6">
-        <v>46269.70987298611</v>
+        <v>46269.71298532408</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -1875,7 +1902,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B11" s="29">
         <v>45.6</v>
@@ -1895,7 +1922,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="B12" s="29">
         <v>49.03</v>
@@ -1978,7 +2005,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="6">
-        <v>46269.70987310185</v>
+        <v>46269.712985439815</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2144,7 +2171,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="6">
-        <v>46269.709873125</v>
+        <v>46269.71298545139</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2220,7 +2247,7 @@
   <sheetPr>
     <tabColor rgb="FF1F8A96"/>
   </sheetPr>
-  <dimension ref="A1:R28"/>
+  <dimension ref="A1:CX28"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -2230,6 +2257,7 @@
     <col min="6" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="14" customWidth="1"/>
     <col min="12" max="18" width="7" customWidth="1"/>
+    <col min="102" max="102" width="3" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
@@ -2291,7 +2319,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="6">
-        <v>46269.70987305556</v>
+        <v>46269.71298539352</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
@@ -2350,7 +2378,7 @@
         <f>Q6+1</f>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:102" x14ac:dyDescent="0.25">
       <c r="A7" s="23" t="s">
         <v>52</v>
       </c>
@@ -2363,6 +2391,9 @@
       <c r="D7" s="25">
         <f>K7</f>
       </c>
+      <c r="F7" s="23" t="s">
+        <v>53</v>
+      </c>
       <c r="G7" s="24">
         <f>B10</f>
       </c>
@@ -2378,10 +2409,13 @@
       <c r="K7" s="25">
         <f>D10+D11+D12</f>
       </c>
-    </row>
-    <row r="8" spans="6:18" x14ac:dyDescent="0.25">
+      <c r="CX7" s="23" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" spans="6:102" x14ac:dyDescent="0.25">
       <c r="F8" s="26" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="L8" s="27">
         <v>1</v>
@@ -2404,37 +2438,43 @@
       <c r="R8" s="27">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="CX8" s="26" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="9" spans="1:102" x14ac:dyDescent="0.25">
       <c r="A9" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="F9" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="L9" s="28">
+        <v>10</v>
+      </c>
+      <c r="M9" s="28">
+        <v>10</v>
+      </c>
+      <c r="N9" s="28">
+        <v>10</v>
+      </c>
+      <c r="O9" s="28">
+        <v>10</v>
+      </c>
+      <c r="P9" s="28">
+        <v>10</v>
+      </c>
+      <c r="Q9" s="28">
+        <v>10</v>
+      </c>
+      <c r="R9" s="28">
+        <v>10</v>
+      </c>
+      <c r="CX9" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="F9" s="26" t="s">
-        <v>55</v>
-      </c>
-      <c r="L9" s="28">
-        <v>10</v>
-      </c>
-      <c r="M9" s="28">
-        <v>10</v>
-      </c>
-      <c r="N9" s="28">
-        <v>10</v>
-      </c>
-      <c r="O9" s="28">
-        <v>10</v>
-      </c>
-      <c r="P9" s="28">
-        <v>10</v>
-      </c>
-      <c r="Q9" s="28">
-        <v>10</v>
-      </c>
-      <c r="R9" s="28">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="2:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="2:102" x14ac:dyDescent="0.25">
       <c r="B10" s="21">
         <f>SUM(L10:R10)</f>
       </c>
@@ -2445,7 +2485,7 @@
         <f>'Rate Tables'!C7</f>
       </c>
       <c r="F10" s="8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="L10" s="21">
         <f>IF(L$6="","",IF(WEEKDAY(L$6,1)=1,0,MIN(10,L9)*L8))</f>
@@ -2468,8 +2508,11 @@
       <c r="R10" s="21">
         <f>IF(R$6="","",IF(WEEKDAY(R$6,1)=1,0,MIN(10,R9)*R8))</f>
       </c>
-    </row>
-    <row r="11" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="CX10" s="8" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="11" spans="2:102" x14ac:dyDescent="0.25">
       <c r="B11" s="21">
         <f>SUM(L11:R11)</f>
       </c>
@@ -2480,7 +2523,7 @@
         <f>'Rate Tables'!D7</f>
       </c>
       <c r="F11" s="8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="L11" s="21">
         <f>IF(L$6="","",IF(WEEKDAY(L$6,1)=1,0,MAX(0,L9-10)*L8))</f>
@@ -2503,8 +2546,11 @@
       <c r="R11" s="21">
         <f>IF(R$6="","",IF(WEEKDAY(R$6,1)=1,0,MAX(0,R9-10)*R8))</f>
       </c>
-    </row>
-    <row r="12" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="CX11" s="8" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="12" spans="2:102" x14ac:dyDescent="0.25">
       <c r="B12" s="21">
         <f>SUM(L12:R12)</f>
       </c>
@@ -2515,7 +2561,7 @@
         <f>'Rate Tables'!E7</f>
       </c>
       <c r="F12" s="8" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="L12" s="21">
         <f>IF(L$6="","",IF(WEEKDAY(L$6,1)=1,L9*L8,0))</f>
@@ -2538,8 +2584,11 @@
       <c r="R12" s="21">
         <f>IF(R$6="","",IF(WEEKDAY(R$6,1)=1,R9*R8,0))</f>
       </c>
-    </row>
-    <row r="13" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="CX12" s="8" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="13" spans="2:102" x14ac:dyDescent="0.25">
       <c r="B13" s="21">
         <f>SUM(L13:R13)</f>
       </c>
@@ -2550,7 +2599,7 @@
         <v>140</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="L13" s="19">
         <v>1</v>
@@ -2573,8 +2622,11 @@
       <c r="R13" s="19">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="CX13" s="8" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="14" spans="1:102" x14ac:dyDescent="0.25">
       <c r="A14" s="23" t="s">
         <v>52</v>
       </c>
@@ -2587,6 +2639,9 @@
       <c r="D14" s="25">
         <f>K14</f>
       </c>
+      <c r="F14" s="23" t="s">
+        <v>53</v>
+      </c>
       <c r="G14" s="24">
         <f>B17</f>
       </c>
@@ -2602,10 +2657,13 @@
       <c r="K14" s="25">
         <f>D17+D18+D19</f>
       </c>
-    </row>
-    <row r="15" spans="6:18" x14ac:dyDescent="0.25">
+      <c r="CX14" s="23" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="15" spans="6:102" x14ac:dyDescent="0.25">
       <c r="F15" s="26" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="L15" s="27">
         <v>1</v>
@@ -2628,13 +2686,16 @@
       <c r="R15" s="27">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="CX15" s="26" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="16" spans="1:102" x14ac:dyDescent="0.25">
       <c r="A16" s="26" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F16" s="26" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="L16" s="28">
         <v>10</v>
@@ -2657,8 +2718,11 @@
       <c r="R16" s="28">
         <v>10</v>
       </c>
-    </row>
-    <row r="17" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="CX16" s="26" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="17" spans="2:102" x14ac:dyDescent="0.25">
       <c r="B17" s="21">
         <f>SUM(L17:R17)</f>
       </c>
@@ -2669,7 +2733,7 @@
         <f>'Rate Tables'!C8</f>
       </c>
       <c r="F17" s="8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="L17" s="21">
         <f>IF(L$6="","",IF(WEEKDAY(L$6,1)=1,0,MIN(10,L16)*L15))</f>
@@ -2692,8 +2756,11 @@
       <c r="R17" s="21">
         <f>IF(R$6="","",IF(WEEKDAY(R$6,1)=1,0,MIN(10,R16)*R15))</f>
       </c>
-    </row>
-    <row r="18" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="CX17" s="8" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="18" spans="2:102" x14ac:dyDescent="0.25">
       <c r="B18" s="21">
         <f>SUM(L18:R18)</f>
       </c>
@@ -2704,7 +2771,7 @@
         <f>'Rate Tables'!D8</f>
       </c>
       <c r="F18" s="8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="L18" s="21">
         <f>IF(L$6="","",IF(WEEKDAY(L$6,1)=1,0,MAX(0,L16-10)*L15))</f>
@@ -2727,8 +2794,11 @@
       <c r="R18" s="21">
         <f>IF(R$6="","",IF(WEEKDAY(R$6,1)=1,0,MAX(0,R16-10)*R15))</f>
       </c>
-    </row>
-    <row r="19" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="CX18" s="8" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="19" spans="2:102" x14ac:dyDescent="0.25">
       <c r="B19" s="21">
         <f>SUM(L19:R19)</f>
       </c>
@@ -2739,7 +2809,7 @@
         <f>'Rate Tables'!E8</f>
       </c>
       <c r="F19" s="8" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="L19" s="21">
         <f>IF(L$6="","",IF(WEEKDAY(L$6,1)=1,L16*L15,0))</f>
@@ -2762,8 +2832,11 @@
       <c r="R19" s="21">
         <f>IF(R$6="","",IF(WEEKDAY(R$6,1)=1,R16*R15,0))</f>
       </c>
-    </row>
-    <row r="20" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="CX19" s="8" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="20" spans="2:102" x14ac:dyDescent="0.25">
       <c r="B20" s="21">
         <f>SUM(L20:R20)</f>
       </c>
@@ -2774,7 +2847,7 @@
         <v>140</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="L20" s="19">
         <v>1</v>
@@ -2797,8 +2870,11 @@
       <c r="R20" s="19">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="CX20" s="8" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="21" spans="1:102" x14ac:dyDescent="0.25">
       <c r="A21" s="23" t="s">
         <v>52</v>
       </c>
@@ -2811,6 +2887,9 @@
       <c r="D21" s="25">
         <f>K21</f>
       </c>
+      <c r="F21" s="23" t="s">
+        <v>53</v>
+      </c>
       <c r="G21" s="24">
         <f>B24</f>
       </c>
@@ -2826,10 +2905,13 @@
       <c r="K21" s="25">
         <f>D24+D25+D26</f>
       </c>
-    </row>
-    <row r="22" spans="6:18" x14ac:dyDescent="0.25">
+      <c r="CX21" s="23" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="22" spans="6:102" x14ac:dyDescent="0.25">
       <c r="F22" s="26" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="L22" s="27">
         <v>1</v>
@@ -2852,13 +2934,16 @@
       <c r="R22" s="27">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="CX22" s="26" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="23" spans="1:102" x14ac:dyDescent="0.25">
       <c r="A23" s="26" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F23" s="26" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="L23" s="28">
         <v>10</v>
@@ -2881,8 +2966,11 @@
       <c r="R23" s="28">
         <v>10</v>
       </c>
-    </row>
-    <row r="24" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="CX23" s="26" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="24" spans="2:102" x14ac:dyDescent="0.25">
       <c r="B24" s="21">
         <f>SUM(L24:R24)</f>
       </c>
@@ -2893,7 +2981,7 @@
         <f>'Rate Tables'!C9</f>
       </c>
       <c r="F24" s="8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="L24" s="21">
         <f>IF(L$6="","",IF(OR(WEEKDAY(L$6,1)=1,WEEKDAY(L$6,1)=7),0,MIN(8,L23)*L22))</f>
@@ -2916,8 +3004,11 @@
       <c r="R24" s="21">
         <f>IF(R$6="","",IF(OR(WEEKDAY(R$6,1)=1,WEEKDAY(R$6,1)=7),0,MIN(8,R23)*R22))</f>
       </c>
-    </row>
-    <row r="25" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="CX24" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="25" spans="2:102" x14ac:dyDescent="0.25">
       <c r="B25" s="21">
         <f>SUM(L25:R25)</f>
       </c>
@@ -2928,7 +3019,7 @@
         <f>'Rate Tables'!D9</f>
       </c>
       <c r="F25" s="8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="L25" s="21">
         <f>IF(L$6="","",IF(WEEKDAY(L$6,1)=1,0,IF(WEEKDAY(L$6,1)=7,L23*L22,MAX(0,L23-8)*L22)))</f>
@@ -2951,8 +3042,11 @@
       <c r="R25" s="21">
         <f>IF(R$6="","",IF(WEEKDAY(R$6,1)=1,0,IF(WEEKDAY(R$6,1)=7,R23*R22,MAX(0,R23-8)*R22)))</f>
       </c>
-    </row>
-    <row r="26" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="CX25" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="26" spans="2:102" x14ac:dyDescent="0.25">
       <c r="B26" s="21">
         <f>SUM(L26:R26)</f>
       </c>
@@ -2963,7 +3057,7 @@
         <f>'Rate Tables'!E9</f>
       </c>
       <c r="F26" s="8" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="L26" s="21">
         <f>IF(L$6="","",IF(WEEKDAY(L$6,1)=1,L23*L22,0))</f>
@@ -2986,8 +3080,11 @@
       <c r="R26" s="21">
         <f>IF(R$6="","",IF(WEEKDAY(R$6,1)=1,R23*R22,0))</f>
       </c>
-    </row>
-    <row r="27" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="CX26" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="27" spans="2:102" x14ac:dyDescent="0.25">
       <c r="B27" s="21">
         <f>SUM(L27:R27)</f>
       </c>
@@ -2998,7 +3095,7 @@
         <v>140</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="L27" s="19">
         <v>1</v>
@@ -3020,6 +3117,9 @@
       </c>
       <c r="R27" s="19">
         <v>1</v>
+      </c>
+      <c r="CX27" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -3070,7 +3170,7 @@
   <sheetPr>
     <tabColor rgb="FF1F8A96"/>
   </sheetPr>
-  <dimension ref="A1:R14"/>
+  <dimension ref="A1:CX14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -3080,6 +3180,7 @@
     <col min="6" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="14" customWidth="1"/>
     <col min="12" max="18" width="7" customWidth="1"/>
+    <col min="102" max="102" width="3" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
@@ -3141,7 +3242,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="6">
-        <v>46269.709873078704</v>
+        <v>46269.71298541667</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
@@ -3200,7 +3301,7 @@
         <f>Q6+1</f>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:102" x14ac:dyDescent="0.25">
       <c r="A7" s="23" t="s">
         <v>52</v>
       </c>
@@ -3213,6 +3314,9 @@
       <c r="D7" s="25">
         <f>K7</f>
       </c>
+      <c r="F7" s="23" t="s">
+        <v>53</v>
+      </c>
       <c r="G7" s="24">
         <f>B10</f>
       </c>
@@ -3228,10 +3332,13 @@
       <c r="K7" s="25">
         <f>D10+D11+D12</f>
       </c>
-    </row>
-    <row r="8" spans="6:18" x14ac:dyDescent="0.25">
+      <c r="CX7" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8" spans="6:102" x14ac:dyDescent="0.25">
       <c r="F8" s="26" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="L8" s="27">
         <v>1</v>
@@ -3254,13 +3361,16 @@
       <c r="R8" s="27">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="CX8" s="26" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" spans="1:102" x14ac:dyDescent="0.25">
       <c r="A9" s="26" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F9" s="26" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="L9" s="28">
         <v>10</v>
@@ -3283,8 +3393,11 @@
       <c r="R9" s="28">
         <v>10</v>
       </c>
-    </row>
-    <row r="10" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="CX9" s="26" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10" spans="2:102" x14ac:dyDescent="0.25">
       <c r="B10" s="21">
         <f>SUM(L10:R10)</f>
       </c>
@@ -3295,7 +3408,7 @@
         <f>'Rate Tables'!C10</f>
       </c>
       <c r="F10" s="8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="L10" s="21">
         <f>IF(L$6="","",IF(OR(WEEKDAY(L$6,1)=1,WEEKDAY(L$6,1)=7),0,MIN(8,L9)*L8))</f>
@@ -3318,8 +3431,11 @@
       <c r="R10" s="21">
         <f>IF(R$6="","",IF(OR(WEEKDAY(R$6,1)=1,WEEKDAY(R$6,1)=7),0,MIN(8,R9)*R8))</f>
       </c>
-    </row>
-    <row r="11" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="CX10" s="8" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="11" spans="2:102" x14ac:dyDescent="0.25">
       <c r="B11" s="21">
         <f>SUM(L11:R11)</f>
       </c>
@@ -3330,7 +3446,7 @@
         <f>'Rate Tables'!D10</f>
       </c>
       <c r="F11" s="8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="L11" s="21">
         <f>IF(L$6="","",IF(WEEKDAY(L$6,1)=1,0,IF(WEEKDAY(L$6,1)=7,L9*L8,MAX(0,L9-8)*L8)))</f>
@@ -3353,8 +3469,11 @@
       <c r="R11" s="21">
         <f>IF(R$6="","",IF(WEEKDAY(R$6,1)=1,0,IF(WEEKDAY(R$6,1)=7,R9*R8,MAX(0,R9-8)*R8)))</f>
       </c>
-    </row>
-    <row r="12" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="CX11" s="8" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="12" spans="2:102" x14ac:dyDescent="0.25">
       <c r="B12" s="21">
         <f>SUM(L12:R12)</f>
       </c>
@@ -3365,7 +3484,7 @@
         <f>'Rate Tables'!E10</f>
       </c>
       <c r="F12" s="8" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="L12" s="21">
         <f>IF(L$6="","",IF(WEEKDAY(L$6,1)=1,L9*L8,0))</f>
@@ -3388,8 +3507,11 @@
       <c r="R12" s="21">
         <f>IF(R$6="","",IF(WEEKDAY(R$6,1)=1,R9*R8,0))</f>
       </c>
-    </row>
-    <row r="13" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="CX12" s="8" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="13" spans="2:102" x14ac:dyDescent="0.25">
       <c r="B13" s="21">
         <f>SUM(L13:R13)</f>
       </c>
@@ -3400,7 +3522,7 @@
         <v>130</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="L13" s="19">
         <v>1</v>
@@ -3422,6 +3544,9 @@
       </c>
       <c r="R13" s="19">
         <v>1</v>
+      </c>
+      <c r="CX13" s="8" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -3472,7 +3597,7 @@
   <sheetPr>
     <tabColor rgb="FF1F8A96"/>
   </sheetPr>
-  <dimension ref="A1:R28"/>
+  <dimension ref="A1:CX28"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -3482,6 +3607,7 @@
     <col min="6" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="14" customWidth="1"/>
     <col min="12" max="18" width="7" customWidth="1"/>
+    <col min="102" max="102" width="3" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
@@ -3543,7 +3669,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="6">
-        <v>46269.709873078704</v>
+        <v>46269.71298541667</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
@@ -3602,7 +3728,7 @@
         <f>Q6+1</f>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:102" x14ac:dyDescent="0.25">
       <c r="A7" s="23" t="s">
         <v>52</v>
       </c>
@@ -3610,11 +3736,14 @@
         <f>G7+H7+I7</f>
       </c>
       <c r="C7" s="23" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D7" s="25">
         <f>K7</f>
       </c>
+      <c r="F7" s="23" t="s">
+        <v>53</v>
+      </c>
       <c r="G7" s="24">
         <f>B10</f>
       </c>
@@ -3630,10 +3759,13 @@
       <c r="K7" s="25">
         <f>D10+D11+D12</f>
       </c>
-    </row>
-    <row r="8" spans="6:18" x14ac:dyDescent="0.25">
+      <c r="CX7" s="23" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="8" spans="6:102" x14ac:dyDescent="0.25">
       <c r="F8" s="26" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="L8" s="27">
         <v>4</v>
@@ -3656,13 +3788,16 @@
       <c r="R8" s="27">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="CX8" s="26" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:102" x14ac:dyDescent="0.25">
       <c r="A9" s="26" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F9" s="26" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="L9" s="28">
         <v>10</v>
@@ -3685,8 +3820,11 @@
       <c r="R9" s="28">
         <v>10</v>
       </c>
-    </row>
-    <row r="10" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="CX9" s="26" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" spans="2:102" x14ac:dyDescent="0.25">
       <c r="B10" s="21">
         <f>SUM(L10:R10)</f>
       </c>
@@ -3697,7 +3835,7 @@
         <f>'Rate Tables'!C11</f>
       </c>
       <c r="F10" s="8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="L10" s="21">
         <f>IF(L$6="","",IF(OR(WEEKDAY(L$6,1)=1,WEEKDAY(L$6,1)=7),0,MIN(8,L9)*L8))</f>
@@ -3720,8 +3858,11 @@
       <c r="R10" s="21">
         <f>IF(R$6="","",IF(OR(WEEKDAY(R$6,1)=1,WEEKDAY(R$6,1)=7),0,MIN(8,R9)*R8))</f>
       </c>
-    </row>
-    <row r="11" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="CX10" s="8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="11" spans="2:102" x14ac:dyDescent="0.25">
       <c r="B11" s="21">
         <f>SUM(L11:R11)</f>
       </c>
@@ -3732,7 +3873,7 @@
         <f>'Rate Tables'!D11</f>
       </c>
       <c r="F11" s="8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="L11" s="21">
         <f>IF(L$6="","",IF(WEEKDAY(L$6,1)=1,0,IF(WEEKDAY(L$6,1)=7,L9*L8,MAX(0,L9-8)*L8)))</f>
@@ -3755,8 +3896,11 @@
       <c r="R11" s="21">
         <f>IF(R$6="","",IF(WEEKDAY(R$6,1)=1,0,IF(WEEKDAY(R$6,1)=7,R9*R8,MAX(0,R9-8)*R8)))</f>
       </c>
-    </row>
-    <row r="12" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="CX11" s="8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="12" spans="2:102" x14ac:dyDescent="0.25">
       <c r="B12" s="21">
         <f>SUM(L12:R12)</f>
       </c>
@@ -3767,7 +3911,7 @@
         <f>'Rate Tables'!E11</f>
       </c>
       <c r="F12" s="8" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="L12" s="21">
         <f>IF(L$6="","",IF(WEEKDAY(L$6,1)=1,L9*L8,0))</f>
@@ -3790,8 +3934,11 @@
       <c r="R12" s="21">
         <f>IF(R$6="","",IF(WEEKDAY(R$6,1)=1,R9*R8,0))</f>
       </c>
-    </row>
-    <row r="13" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="CX12" s="8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13" spans="2:102" x14ac:dyDescent="0.25">
       <c r="B13" s="21">
         <f>SUM(L13:R13)</f>
       </c>
@@ -3802,7 +3949,7 @@
         <v>130</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="L13" s="19">
         <v>4</v>
@@ -3825,20 +3972,26 @@
       <c r="R13" s="19">
         <v>4</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="CX13" s="8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="14" spans="1:102" x14ac:dyDescent="0.25">
       <c r="A14" s="23" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B14" s="24">
         <f>G14+H14+I14</f>
       </c>
       <c r="C14" s="23" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D14" s="25">
         <f>K14</f>
       </c>
+      <c r="F14" s="23" t="s">
+        <v>53</v>
+      </c>
       <c r="G14" s="24">
         <f>B17</f>
       </c>
@@ -3854,10 +4007,13 @@
       <c r="K14" s="25">
         <f>D17+D18+D19</f>
       </c>
-    </row>
-    <row r="15" spans="6:18" x14ac:dyDescent="0.25">
+      <c r="CX14" s="23" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="15" spans="6:102" x14ac:dyDescent="0.25">
       <c r="F15" s="26" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="L15" s="27">
         <v>2</v>
@@ -3880,13 +4036,16 @@
       <c r="R15" s="27">
         <v>2</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="CX15" s="26" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="16" spans="1:102" x14ac:dyDescent="0.25">
       <c r="A16" s="26" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F16" s="26" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="L16" s="28">
         <v>10</v>
@@ -3909,8 +4068,11 @@
       <c r="R16" s="28">
         <v>10</v>
       </c>
-    </row>
-    <row r="17" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="CX16" s="26" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="17" spans="2:102" x14ac:dyDescent="0.25">
       <c r="B17" s="21">
         <f>SUM(L17:R17)</f>
       </c>
@@ -3921,7 +4083,7 @@
         <f>'Rate Tables'!C11</f>
       </c>
       <c r="F17" s="8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="L17" s="21">
         <f>IF(L$6="","",IF(OR(WEEKDAY(L$6,1)=1,WEEKDAY(L$6,1)=7),0,MIN(8,L16)*L15))</f>
@@ -3944,8 +4106,11 @@
       <c r="R17" s="21">
         <f>IF(R$6="","",IF(OR(WEEKDAY(R$6,1)=1,WEEKDAY(R$6,1)=7),0,MIN(8,R16)*R15))</f>
       </c>
-    </row>
-    <row r="18" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="CX17" s="8" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="18" spans="2:102" x14ac:dyDescent="0.25">
       <c r="B18" s="21">
         <f>SUM(L18:R18)</f>
       </c>
@@ -3956,7 +4121,7 @@
         <f>'Rate Tables'!D11</f>
       </c>
       <c r="F18" s="8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="L18" s="21">
         <f>IF(L$6="","",IF(WEEKDAY(L$6,1)=1,0,IF(WEEKDAY(L$6,1)=7,L16*L15,MAX(0,L16-8)*L15)))</f>
@@ -3979,8 +4144,11 @@
       <c r="R18" s="21">
         <f>IF(R$6="","",IF(WEEKDAY(R$6,1)=1,0,IF(WEEKDAY(R$6,1)=7,R16*R15,MAX(0,R16-8)*R15)))</f>
       </c>
-    </row>
-    <row r="19" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="CX18" s="8" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="19" spans="2:102" x14ac:dyDescent="0.25">
       <c r="B19" s="21">
         <f>SUM(L19:R19)</f>
       </c>
@@ -3991,7 +4159,7 @@
         <f>'Rate Tables'!E11</f>
       </c>
       <c r="F19" s="8" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="L19" s="21">
         <f>IF(L$6="","",IF(WEEKDAY(L$6,1)=1,L16*L15,0))</f>
@@ -4014,8 +4182,11 @@
       <c r="R19" s="21">
         <f>IF(R$6="","",IF(WEEKDAY(R$6,1)=1,R16*R15,0))</f>
       </c>
-    </row>
-    <row r="20" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="CX19" s="8" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="20" spans="2:102" x14ac:dyDescent="0.25">
       <c r="B20" s="21">
         <f>SUM(L20:R20)</f>
       </c>
@@ -4026,7 +4197,7 @@
         <v>130</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="L20" s="19">
         <v>0</v>
@@ -4049,8 +4220,11 @@
       <c r="R20" s="19">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="CX20" s="8" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="21" spans="1:102" x14ac:dyDescent="0.25">
       <c r="A21" s="23" t="s">
         <v>52</v>
       </c>
@@ -4058,11 +4232,14 @@
         <f>G21+H21+I21</f>
       </c>
       <c r="C21" s="23" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="D21" s="25">
         <f>K21</f>
       </c>
+      <c r="F21" s="23" t="s">
+        <v>53</v>
+      </c>
       <c r="G21" s="24">
         <f>B24</f>
       </c>
@@ -4078,10 +4255,13 @@
       <c r="K21" s="25">
         <f>D24+D25+D26</f>
       </c>
-    </row>
-    <row r="22" spans="6:18" x14ac:dyDescent="0.25">
+      <c r="CX21" s="23" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="22" spans="6:102" x14ac:dyDescent="0.25">
       <c r="F22" s="26" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="L22" s="27">
         <v>3</v>
@@ -4104,13 +4284,16 @@
       <c r="R22" s="27">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="CX22" s="26" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="23" spans="1:102" x14ac:dyDescent="0.25">
       <c r="A23" s="26" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F23" s="26" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="L23" s="28">
         <v>10</v>
@@ -4133,8 +4316,11 @@
       <c r="R23" s="28">
         <v>10</v>
       </c>
-    </row>
-    <row r="24" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="CX23" s="26" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="24" spans="2:102" x14ac:dyDescent="0.25">
       <c r="B24" s="21">
         <f>SUM(L24:R24)</f>
       </c>
@@ -4145,7 +4331,7 @@
         <f>'Rate Tables'!C12</f>
       </c>
       <c r="F24" s="8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="L24" s="21">
         <f>IF(L$6="","",IF(OR(WEEKDAY(L$6,1)=1,WEEKDAY(L$6,1)=7),0,MIN(8,L23)*L22))</f>
@@ -4168,8 +4354,11 @@
       <c r="R24" s="21">
         <f>IF(R$6="","",IF(OR(WEEKDAY(R$6,1)=1,WEEKDAY(R$6,1)=7),0,MIN(8,R23)*R22))</f>
       </c>
-    </row>
-    <row r="25" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="CX24" s="8" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="25" spans="2:102" x14ac:dyDescent="0.25">
       <c r="B25" s="21">
         <f>SUM(L25:R25)</f>
       </c>
@@ -4180,7 +4369,7 @@
         <f>'Rate Tables'!D12</f>
       </c>
       <c r="F25" s="8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="L25" s="21">
         <f>IF(L$6="","",IF(WEEKDAY(L$6,1)=1,0,IF(WEEKDAY(L$6,1)=7,L23*L22,MAX(0,L23-8)*L22)))</f>
@@ -4203,8 +4392,11 @@
       <c r="R25" s="21">
         <f>IF(R$6="","",IF(WEEKDAY(R$6,1)=1,0,IF(WEEKDAY(R$6,1)=7,R23*R22,MAX(0,R23-8)*R22)))</f>
       </c>
-    </row>
-    <row r="26" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="CX25" s="8" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="26" spans="2:102" x14ac:dyDescent="0.25">
       <c r="B26" s="21">
         <f>SUM(L26:R26)</f>
       </c>
@@ -4215,7 +4407,7 @@
         <f>'Rate Tables'!E12</f>
       </c>
       <c r="F26" s="8" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="L26" s="21">
         <f>IF(L$6="","",IF(WEEKDAY(L$6,1)=1,L23*L22,0))</f>
@@ -4238,8 +4430,11 @@
       <c r="R26" s="21">
         <f>IF(R$6="","",IF(WEEKDAY(R$6,1)=1,R23*R22,0))</f>
       </c>
-    </row>
-    <row r="27" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="CX26" s="8" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="27" spans="2:102" x14ac:dyDescent="0.25">
       <c r="B27" s="21">
         <f>SUM(L27:R27)</f>
       </c>
@@ -4250,7 +4445,7 @@
         <v>130</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="L27" s="19">
         <v>3</v>
@@ -4272,6 +4467,9 @@
       </c>
       <c r="R27" s="19">
         <v>3</v>
+      </c>
+      <c r="CX27" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -4322,7 +4520,7 @@
   <sheetPr>
     <tabColor rgb="FF1F8A96"/>
   </sheetPr>
-  <dimension ref="A1:R14"/>
+  <dimension ref="A1:CX14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -4332,6 +4530,7 @@
     <col min="6" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="14" customWidth="1"/>
     <col min="12" max="18" width="7" customWidth="1"/>
+    <col min="102" max="102" width="3" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
@@ -4393,7 +4592,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="6">
-        <v>46269.70987310185</v>
+        <v>46269.71298542824</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
@@ -4452,7 +4651,7 @@
         <f>Q6+1</f>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:102" x14ac:dyDescent="0.25">
       <c r="A7" s="23" t="s">
         <v>52</v>
       </c>
@@ -4460,11 +4659,14 @@
         <f>G7+H7+I7</f>
       </c>
       <c r="C7" s="23" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="D7" s="25">
         <f>K7</f>
       </c>
+      <c r="F7" s="23" t="s">
+        <v>53</v>
+      </c>
       <c r="G7" s="24">
         <f>B10</f>
       </c>
@@ -4480,10 +4682,13 @@
       <c r="K7" s="25">
         <f>D10+D11+D12</f>
       </c>
-    </row>
-    <row r="8" spans="6:18" x14ac:dyDescent="0.25">
+      <c r="CX7" s="23" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="8" spans="6:102" x14ac:dyDescent="0.25">
       <c r="F8" s="26" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="L8" s="27">
         <v>1</v>
@@ -4506,13 +4711,16 @@
       <c r="R8" s="27">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="CX8" s="26" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:102" x14ac:dyDescent="0.25">
       <c r="A9" s="26" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F9" s="26" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="L9" s="28">
         <v>10</v>
@@ -4535,8 +4743,11 @@
       <c r="R9" s="28">
         <v>10</v>
       </c>
-    </row>
-    <row r="10" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="CX9" s="26" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="10" spans="2:102" x14ac:dyDescent="0.25">
       <c r="B10" s="21">
         <f>SUM(L10:R10)</f>
       </c>
@@ -4547,7 +4758,7 @@
         <f>'Rate Tables'!C11</f>
       </c>
       <c r="F10" s="8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="L10" s="21">
         <f>IF(L$6="","",IF(OR(WEEKDAY(L$6,1)=1,WEEKDAY(L$6,1)=7),0,MIN(8,L9)*L8))</f>
@@ -4570,8 +4781,11 @@
       <c r="R10" s="21">
         <f>IF(R$6="","",IF(OR(WEEKDAY(R$6,1)=1,WEEKDAY(R$6,1)=7),0,MIN(8,R9)*R8))</f>
       </c>
-    </row>
-    <row r="11" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="CX10" s="8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="11" spans="2:102" x14ac:dyDescent="0.25">
       <c r="B11" s="21">
         <f>SUM(L11:R11)</f>
       </c>
@@ -4582,7 +4796,7 @@
         <f>'Rate Tables'!D11</f>
       </c>
       <c r="F11" s="8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="L11" s="21">
         <f>IF(L$6="","",IF(WEEKDAY(L$6,1)=1,0,IF(WEEKDAY(L$6,1)=7,L9*L8,MAX(0,L9-8)*L8)))</f>
@@ -4605,8 +4819,11 @@
       <c r="R11" s="21">
         <f>IF(R$6="","",IF(WEEKDAY(R$6,1)=1,0,IF(WEEKDAY(R$6,1)=7,R9*R8,MAX(0,R9-8)*R8)))</f>
       </c>
-    </row>
-    <row r="12" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="CX11" s="8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="12" spans="2:102" x14ac:dyDescent="0.25">
       <c r="B12" s="21">
         <f>SUM(L12:R12)</f>
       </c>
@@ -4617,7 +4834,7 @@
         <f>'Rate Tables'!E11</f>
       </c>
       <c r="F12" s="8" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="L12" s="21">
         <f>IF(L$6="","",IF(WEEKDAY(L$6,1)=1,L9*L8,0))</f>
@@ -4640,8 +4857,11 @@
       <c r="R12" s="21">
         <f>IF(R$6="","",IF(WEEKDAY(R$6,1)=1,R9*R8,0))</f>
       </c>
-    </row>
-    <row r="13" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="CX12" s="8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="13" spans="2:102" x14ac:dyDescent="0.25">
       <c r="B13" s="21">
         <f>SUM(L13:R13)</f>
       </c>
@@ -4652,7 +4872,7 @@
         <v>130</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="L13" s="19">
         <v>1</v>
@@ -4674,6 +4894,9 @@
       </c>
       <c r="R13" s="19">
         <v>1</v>
+      </c>
+      <c r="CX13" s="8" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -4772,41 +4995,41 @@
         <v>4</v>
       </c>
       <c r="B5" s="6">
-        <v>46269.709873125</v>
+        <v>46269.71298545139</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="C7" s="19">
         <v>1</v>
@@ -4908,41 +5131,41 @@
         <v>4</v>
       </c>
       <c r="B5" s="6">
-        <v>46269.709873125</v>
+        <v>46269.71298545139</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="C7" s="19">
         <v>1</v>
